--- a/Zen_Estate_Combined_Expenses_Q1.xlsx
+++ b/Zen_Estate_Combined_Expenses_Q1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 11 - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D174B0-DE91-407F-905F-086D94CF1588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8856BE-1A56-4652-B3B1-14B3B59C43F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="196">
   <si>
     <t>Opening Balance = 11,52,000/-</t>
   </si>
@@ -585,9 +585,6 @@
     <t>120 Tubes, 8 Flood lights &amp; wire</t>
   </si>
   <si>
-    <t>15th Aug Refreshment, Ballon decoration &amp; banner</t>
-  </si>
-  <si>
     <t>FM Team Uniform</t>
   </si>
   <si>
@@ -619,6 +616,15 @@
   </si>
   <si>
     <t>STP Sludge Transfer Pump</t>
+  </si>
+  <si>
+    <t>15th Aug refreshment &amp; decoration</t>
+  </si>
+  <si>
+    <t>Nursary tree plantation</t>
+  </si>
+  <si>
+    <t>Media Cleaning</t>
   </si>
 </sst>
 </file>
@@ -11030,7 +11036,7 @@
         <v>134</v>
       </c>
       <c r="X131" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y131" s="33"/>
       <c r="Z131" s="33"/>
@@ -11228,8 +11234,8 @@
         <v>95</v>
       </c>
       <c r="P134" s="62">
-        <f>SUM(G133:V133)</f>
-        <v>2205579.98</v>
+        <f>SUM(G133:X133)</f>
+        <v>2242242.98</v>
       </c>
       <c r="Q134" s="20"/>
       <c r="R134" s="63" t="s">
@@ -12334,10 +12340,10 @@
         <v>46188</v>
       </c>
       <c r="AA151" s="111">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="AB151" s="111">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="AC151" s="34"/>
     </row>
@@ -12463,8 +12469,8 @@
         <v>95</v>
       </c>
       <c r="P153" s="62">
-        <f>SUM(G152:W152)</f>
-        <v>2204899.98</v>
+        <f>SUM(G152:AB152)</f>
+        <v>2810825.98</v>
       </c>
       <c r="R153" s="63" t="s">
         <v>85</v>
@@ -13495,10 +13501,10 @@
         <v>170</v>
       </c>
       <c r="W169" s="113" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X169" s="113" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y169" s="113" t="s">
         <v>166</v>
@@ -13702,8 +13708,8 @@
         <v>95</v>
       </c>
       <c r="P172" s="62">
-        <f>SUM(G171:W171)</f>
-        <v>2593066</v>
+        <f>SUM(G171:Y171)</f>
+        <v>2706466</v>
       </c>
       <c r="Q172" s="20"/>
       <c r="R172" s="63" t="s">
@@ -14672,10 +14678,10 @@
         <v>181</v>
       </c>
       <c r="X185" s="113" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y185" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z185" s="33"/>
       <c r="AA185" s="33"/>
@@ -14876,8 +14882,8 @@
         <v>95</v>
       </c>
       <c r="P188" s="62">
-        <f>SUM(G187:W187)</f>
-        <v>2165957</v>
+        <f>SUM(G187:Y187)</f>
+        <v>2190687</v>
       </c>
       <c r="Q188" s="20"/>
       <c r="R188" s="63" t="s">
@@ -15121,27 +15127,62 @@
       <c r="C194" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="D194" s="25"/>
+      <c r="D194" s="25">
+        <v>100000</v>
+      </c>
       <c r="F194" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G194" s="14"/>
-      <c r="H194" s="14"/>
-      <c r="I194" s="14"/>
-      <c r="J194" s="14"/>
-      <c r="K194" s="14"/>
-      <c r="L194" s="14"/>
-      <c r="M194" s="14"/>
-      <c r="N194" s="14"/>
-      <c r="O194" s="14"/>
-      <c r="P194" s="14"/>
-      <c r="Q194" s="14"/>
-      <c r="R194" s="14"/>
+      <c r="G194" s="14">
+        <v>213425</v>
+      </c>
+      <c r="H194" s="15">
+        <v>19121</v>
+      </c>
+      <c r="I194" s="14">
+        <v>204724</v>
+      </c>
+      <c r="J194" s="15">
+        <v>16388</v>
+      </c>
+      <c r="K194" s="14">
+        <v>204013</v>
+      </c>
+      <c r="L194" s="14">
+        <f>SUM(M194:N194)</f>
+        <v>16388</v>
+      </c>
+      <c r="M194" s="14">
+        <v>13657</v>
+      </c>
+      <c r="N194" s="15">
+        <v>2731</v>
+      </c>
+      <c r="O194" s="14">
+        <v>186466</v>
+      </c>
+      <c r="P194" s="14">
+        <v>16388.07</v>
+      </c>
+      <c r="Q194" s="14">
+        <v>309604</v>
+      </c>
+      <c r="R194" s="14">
+        <v>21852.5</v>
+      </c>
       <c r="S194" s="14"/>
-      <c r="T194" s="14"/>
-      <c r="U194" s="14"/>
-      <c r="V194" s="14"/>
-      <c r="W194" s="76"/>
+      <c r="T194" s="14">
+        <v>214017.13</v>
+      </c>
+      <c r="U194" s="14">
+        <v>205207</v>
+      </c>
+      <c r="V194" s="14">
+        <v>99304</v>
+      </c>
+      <c r="W194" s="76">
+        <v>19121</v>
+      </c>
       <c r="X194" s="78"/>
       <c r="Y194" s="78">
         <v>8000</v>
@@ -15185,7 +15226,9 @@
       <c r="C195" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="D195" s="25"/>
+      <c r="D195" s="25">
+        <v>446560</v>
+      </c>
       <c r="F195" s="14" t="s">
         <v>27</v>
       </c>
@@ -15205,7 +15248,9 @@
       <c r="T195" s="14"/>
       <c r="U195" s="14"/>
       <c r="V195" s="14"/>
-      <c r="W195" s="76"/>
+      <c r="W195" s="76">
+        <v>16388</v>
+      </c>
       <c r="X195" s="78"/>
       <c r="Y195" s="93"/>
       <c r="Z195" s="14">
@@ -15247,7 +15292,9 @@
       <c r="C196" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D196" s="25"/>
+      <c r="D196" s="25">
+        <v>249900</v>
+      </c>
       <c r="F196" s="14" t="s">
         <v>27</v>
       </c>
@@ -15267,13 +15314,19 @@
       <c r="T196" s="14"/>
       <c r="U196" s="14"/>
       <c r="V196" s="14"/>
-      <c r="W196" s="76"/>
+      <c r="W196" s="76">
+        <v>2731</v>
+      </c>
       <c r="X196" s="78"/>
       <c r="Y196" s="93"/>
-      <c r="Z196" s="14"/>
+      <c r="Z196" s="14">
+        <v>6000</v>
+      </c>
       <c r="AA196" s="79"/>
       <c r="AB196" s="79"/>
-      <c r="AC196" s="79"/>
+      <c r="AC196" s="79">
+        <v>2000</v>
+      </c>
       <c r="AE196" s="53" t="s">
         <v>119</v>
       </c>
@@ -15302,7 +15355,9 @@
       <c r="C197" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D197" s="25"/>
+      <c r="D197" s="25">
+        <v>272999</v>
+      </c>
       <c r="F197" s="14" t="s">
         <v>27</v>
       </c>
@@ -15357,7 +15412,9 @@
       <c r="C198" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="D198" s="25"/>
+      <c r="D198" s="25">
+        <v>77100</v>
+      </c>
       <c r="F198" s="14" t="s">
         <v>27</v>
       </c>
@@ -15458,7 +15515,9 @@
       <c r="C199" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D199" s="25"/>
+      <c r="D199" s="25">
+        <v>10149</v>
+      </c>
       <c r="F199" s="14" t="s">
         <v>27</v>
       </c>
@@ -15496,53 +15555,97 @@
       <c r="C200" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D200" s="25"/>
+      <c r="D200" s="25">
+        <v>21800</v>
+      </c>
       <c r="F200" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
-      <c r="L200" s="6"/>
+      <c r="G200" s="6">
+        <f>SUM(G194:G199)</f>
+        <v>213425</v>
+      </c>
+      <c r="H200" s="6">
+        <f>SUM(H194:H199)</f>
+        <v>19121</v>
+      </c>
+      <c r="I200" s="6">
+        <f t="shared" ref="I200:L200" si="101">SUM(I194:I199)</f>
+        <v>204724</v>
+      </c>
+      <c r="J200" s="6">
+        <f t="shared" si="101"/>
+        <v>16388</v>
+      </c>
+      <c r="K200" s="6">
+        <f t="shared" si="101"/>
+        <v>204013</v>
+      </c>
+      <c r="L200" s="6">
+        <f t="shared" si="101"/>
+        <v>16388</v>
+      </c>
       <c r="M200" s="6"/>
       <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="6"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="6"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
+      <c r="O200" s="6">
+        <f>SUM(O194:O199)</f>
+        <v>186466</v>
+      </c>
+      <c r="P200" s="6">
+        <f t="shared" ref="P200:V200" si="102">SUM(P194:P199)</f>
+        <v>16388.07</v>
+      </c>
+      <c r="Q200" s="6">
+        <f t="shared" si="102"/>
+        <v>309604</v>
+      </c>
+      <c r="R200" s="6">
+        <f t="shared" si="102"/>
+        <v>21852.5</v>
+      </c>
+      <c r="S200" s="6">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="T200" s="6">
+        <f t="shared" si="102"/>
+        <v>214017.13</v>
+      </c>
+      <c r="U200" s="6">
+        <f t="shared" si="102"/>
+        <v>205207</v>
+      </c>
+      <c r="V200" s="6">
+        <f t="shared" si="102"/>
+        <v>99304</v>
+      </c>
       <c r="W200" s="6">
         <f>SUM(W194:W199)</f>
-        <v>0</v>
+        <v>38240</v>
       </c>
       <c r="X200" s="55">
-        <f t="shared" ref="X200:AC200" si="101">SUM(X194:X199)</f>
+        <f t="shared" ref="X200:AC200" si="103">SUM(X194:X199)</f>
         <v>0</v>
       </c>
       <c r="Y200" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>8000</v>
       </c>
       <c r="Z200" s="55">
-        <f t="shared" si="101"/>
-        <v>21000</v>
+        <f t="shared" si="103"/>
+        <v>27000</v>
       </c>
       <c r="AA200" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AB200" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AC200" s="55">
-        <f t="shared" si="101"/>
-        <v>4500</v>
+        <f t="shared" si="103"/>
+        <v>6500</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="28.8">
@@ -15555,26 +15658,56 @@
       <c r="C201" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="D201" s="25"/>
+      <c r="D201" s="25">
+        <v>30000</v>
+      </c>
       <c r="F201" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="G201" s="39"/>
-      <c r="H201" s="39"/>
-      <c r="I201" s="39"/>
-      <c r="J201" s="39"/>
-      <c r="K201" s="39"/>
-      <c r="L201" s="39"/>
+      <c r="G201" s="39">
+        <v>213424.77</v>
+      </c>
+      <c r="H201" s="39">
+        <v>19121.25</v>
+      </c>
+      <c r="I201" s="39">
+        <v>204724</v>
+      </c>
+      <c r="J201" s="39">
+        <v>16388.07</v>
+      </c>
+      <c r="K201" s="39">
+        <v>204013</v>
+      </c>
+      <c r="L201" s="39">
+        <v>16388.07</v>
+      </c>
       <c r="M201" s="39"/>
       <c r="N201" s="39"/>
-      <c r="O201" s="39"/>
-      <c r="P201" s="39"/>
-      <c r="Q201" s="39"/>
-      <c r="R201" s="39"/>
-      <c r="S201" s="39"/>
-      <c r="T201" s="39"/>
-      <c r="U201" s="39"/>
-      <c r="V201" s="39"/>
+      <c r="O201" s="39">
+        <v>186466</v>
+      </c>
+      <c r="P201" s="39">
+        <v>16388.07</v>
+      </c>
+      <c r="Q201" s="39">
+        <v>309604.52</v>
+      </c>
+      <c r="R201" s="39">
+        <v>21852.5</v>
+      </c>
+      <c r="S201" s="39">
+        <v>212179.1</v>
+      </c>
+      <c r="T201" s="39">
+        <v>214017.1</v>
+      </c>
+      <c r="U201" s="39">
+        <v>205206.6</v>
+      </c>
+      <c r="V201" s="39">
+        <v>99303.81</v>
+      </c>
       <c r="W201" s="20"/>
       <c r="X201" s="20"/>
       <c r="Y201" s="20"/>
@@ -15593,33 +15726,35 @@
       <c r="C202" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="D202" s="25"/>
+      <c r="D202" s="25">
+        <v>41979</v>
+      </c>
       <c r="F202" s="46" t="s">
         <v>87</v>
       </c>
       <c r="G202" s="54">
-        <f t="shared" ref="G202" si="102">(G201-G200)</f>
-        <v>0</v>
+        <f t="shared" ref="G202" si="104">(G201-G200)</f>
+        <v>-0.23000000001047738</v>
       </c>
       <c r="H202" s="54">
         <f>(H201-H200)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I202" s="54">
-        <f t="shared" ref="I202:L202" si="103">(I201-I200)</f>
+        <f t="shared" ref="I202:L202" si="105">(I201-I200)</f>
         <v>0</v>
       </c>
       <c r="J202" s="54">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <f t="shared" si="105"/>
+        <v>6.9999999999708962E-2</v>
       </c>
       <c r="K202" s="54">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="L202" s="54">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <f t="shared" si="105"/>
+        <v>6.9999999999708962E-2</v>
       </c>
       <c r="M202" s="54"/>
       <c r="N202" s="54"/>
@@ -15632,28 +15767,28 @@
         <v>0</v>
       </c>
       <c r="Q202" s="54">
-        <f t="shared" ref="Q202:R202" si="104">(Q201-Q200)</f>
-        <v>0</v>
+        <f t="shared" ref="Q202:R202" si="106">(Q201-Q200)</f>
+        <v>0.52000000001862645</v>
       </c>
       <c r="R202" s="54">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="S202" s="54">
         <f>(S201-S200)</f>
-        <v>0</v>
+        <v>212179.1</v>
       </c>
       <c r="T202" s="54">
-        <f t="shared" ref="T202:U202" si="105">(T201-T200)</f>
-        <v>0</v>
+        <f t="shared" ref="T202:U202" si="107">(T201-T200)</f>
+        <v>-2.9999999998835847E-2</v>
       </c>
       <c r="U202" s="54">
-        <f t="shared" si="105"/>
-        <v>0</v>
+        <f t="shared" si="107"/>
+        <v>-0.39999999999417923</v>
       </c>
       <c r="V202" s="54">
         <f>(V201-V200)</f>
-        <v>0</v>
+        <v>-0.19000000000232831</v>
       </c>
       <c r="W202" s="31"/>
       <c r="X202" s="31"/>
@@ -15663,7 +15798,7 @@
       <c r="AB202" s="31"/>
       <c r="AC202" s="31"/>
     </row>
-    <row r="203" spans="1:45" ht="57.6">
+    <row r="203" spans="1:45" ht="43.2">
       <c r="A203" s="25">
         <v>10</v>
       </c>
@@ -15673,7 +15808,9 @@
       <c r="C203" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="D203" s="25"/>
+      <c r="D203" s="25">
+        <v>68570</v>
+      </c>
       <c r="F203" s="7" t="s">
         <v>4</v>
       </c>
@@ -15716,23 +15853,27 @@
       <c r="S203" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T203" s="32"/>
-      <c r="U203" s="32"/>
-      <c r="V203" s="32" t="s">
-        <v>182</v>
+      <c r="T203" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="U203" s="113" t="s">
+        <v>180</v>
+      </c>
+      <c r="V203" s="113" t="s">
+        <v>184</v>
       </c>
       <c r="W203" s="113" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="X203" s="113" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="Y203" s="113" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z203" s="33"/>
-      <c r="AA203" s="33"/>
-      <c r="AB203" s="33"/>
+        <v>194</v>
+      </c>
+      <c r="Z203" s="113" t="s">
+        <v>195</v>
+      </c>
       <c r="AC203" s="33"/>
     </row>
     <row r="204" spans="1:45">
@@ -15745,7 +15886,9 @@
       <c r="C204" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D204" s="25"/>
+      <c r="D204" s="25">
+        <v>339330</v>
+      </c>
       <c r="F204" s="14" t="s">
         <v>3</v>
       </c>
@@ -15791,10 +15934,10 @@
       <c r="T204" s="19">
         <v>46280</v>
       </c>
-      <c r="U204" s="19">
+      <c r="U204" s="111">
         <v>46280</v>
       </c>
-      <c r="V204" s="19">
+      <c r="V204" s="111">
         <v>46280</v>
       </c>
       <c r="W204" s="111">
@@ -15806,9 +15949,9 @@
       <c r="Y204" s="111">
         <v>46280</v>
       </c>
-      <c r="Z204" s="34"/>
-      <c r="AA204" s="34"/>
-      <c r="AB204" s="34"/>
+      <c r="Z204" s="111">
+        <v>46280</v>
+      </c>
       <c r="AC204" s="34"/>
     </row>
     <row r="205" spans="1:45" ht="15" thickBot="1">
@@ -15821,40 +15964,72 @@
       <c r="C205" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="D205" s="25"/>
+      <c r="D205" s="25">
+        <v>6000</v>
+      </c>
       <c r="F205" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G205" s="49"/>
-      <c r="H205" s="49"/>
-      <c r="I205" s="49"/>
-      <c r="J205" s="49"/>
-      <c r="K205" s="49"/>
-      <c r="L205" s="49"/>
-      <c r="M205" s="49"/>
-      <c r="N205" s="49"/>
-      <c r="O205" s="49"/>
-      <c r="P205" s="49"/>
-      <c r="Q205" s="49"/>
-      <c r="R205" s="49"/>
-      <c r="S205" s="49"/>
-      <c r="T205" s="49"/>
-      <c r="U205" s="49"/>
-      <c r="V205" s="49">
+      <c r="G205" s="49">
+        <v>249900</v>
+      </c>
+      <c r="H205" s="49">
+        <v>446560</v>
+      </c>
+      <c r="I205" s="49">
+        <v>272999</v>
+      </c>
+      <c r="J205" s="49">
+        <v>77100</v>
+      </c>
+      <c r="K205" s="49">
+        <v>100000</v>
+      </c>
+      <c r="L205" s="49">
+        <v>269937</v>
+      </c>
+      <c r="M205" s="49">
+        <v>6000</v>
+      </c>
+      <c r="N205" s="49">
+        <v>10149</v>
+      </c>
+      <c r="O205" s="49">
+        <v>21800</v>
+      </c>
+      <c r="P205" s="49">
+        <v>30000</v>
+      </c>
+      <c r="Q205" s="49">
+        <v>41979</v>
+      </c>
+      <c r="R205" s="49">
+        <v>339330</v>
+      </c>
+      <c r="S205" s="49">
+        <v>68570</v>
+      </c>
+      <c r="T205" s="49">
+        <v>4750</v>
+      </c>
+      <c r="U205" s="112">
+        <v>11965</v>
+      </c>
+      <c r="V205" s="112">
+        <v>5900</v>
+      </c>
+      <c r="W205" s="112">
+        <v>10000</v>
+      </c>
+      <c r="X205" s="112">
         <v>28260</v>
       </c>
-      <c r="W205" s="112">
-        <v>11965</v>
-      </c>
-      <c r="X205" s="112">
-        <v>5900</v>
-      </c>
       <c r="Y205" s="112">
-        <v>10000</v>
-      </c>
-      <c r="Z205" s="20"/>
-      <c r="AA205" s="20"/>
-      <c r="AB205" s="20"/>
+        <v>45000</v>
+      </c>
+      <c r="Z205" s="112">
+        <v>6000</v>
+      </c>
       <c r="AC205" s="20"/>
     </row>
     <row r="206" spans="1:45" ht="43.8" thickBot="1">
@@ -15867,34 +16042,36 @@
       <c r="C206" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D206" s="25"/>
+      <c r="D206" s="25">
+        <v>269937</v>
+      </c>
       <c r="F206" s="57" t="s">
         <v>84</v>
       </c>
       <c r="G206" s="58">
         <f>SUM(G201:V201)</f>
-        <v>0</v>
+        <v>1939076.8600000003</v>
       </c>
       <c r="I206" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J206" s="60" t="b">
-        <f>C195=SUM(G200:V200)-AE204</f>
-        <v>0</v>
+      <c r="J206" s="60">
+        <f>SUM(G200:V200)-AE204</f>
+        <v>1726897.6999999997</v>
       </c>
       <c r="L206" s="67" t="s">
         <v>77</v>
       </c>
       <c r="M206" s="68">
         <f>(G206-J206)</f>
-        <v>0</v>
+        <v>212179.16000000061</v>
       </c>
       <c r="O206" s="61" t="s">
         <v>95</v>
       </c>
       <c r="P206" s="62">
-        <f>SUM(G205:W205)</f>
-        <v>40225</v>
+        <f>SUM(G205:Z205)</f>
+        <v>2046199</v>
       </c>
       <c r="Q206" s="20"/>
       <c r="R206" s="63" t="s">
@@ -15902,7 +16079,7 @@
       </c>
       <c r="S206" s="64">
         <f>SUM(X200:AC200)</f>
-        <v>33500</v>
+        <v>41500</v>
       </c>
       <c r="T206" s="35"/>
       <c r="U206" s="20"/>
@@ -15926,8 +16103,12 @@
       <c r="B208" s="26">
         <v>46203</v>
       </c>
-      <c r="C208" s="27"/>
-      <c r="D208" s="25"/>
+      <c r="C208" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D208" s="25">
+        <v>4750</v>
+      </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="25">
@@ -16511,7 +16692,7 @@
   <sheetData>
     <row r="2" spans="3:4">
       <c r="C2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D2">
         <v>1377415</v>
@@ -16567,7 +16748,7 @@
     </row>
     <row r="9" spans="3:4">
       <c r="C9" s="116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D9">
         <v>23163</v>
@@ -16591,7 +16772,7 @@
     </row>
     <row r="12" spans="3:4" ht="18" customHeight="1">
       <c r="C12" s="116" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12">
         <v>219000</v>
@@ -16599,7 +16780,7 @@
     </row>
     <row r="13" spans="3:4">
       <c r="C13" s="116" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D13">
         <v>169250</v>
@@ -16607,7 +16788,7 @@
     </row>
     <row r="14" spans="3:4">
       <c r="C14" s="116" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D14">
         <v>87108</v>
@@ -16615,7 +16796,7 @@
     </row>
     <row r="15" spans="3:4">
       <c r="C15" s="116" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D15">
         <v>70800</v>
@@ -16623,7 +16804,7 @@
     </row>
     <row r="16" spans="3:4">
       <c r="C16" s="116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D16">
         <v>107500</v>
@@ -16655,7 +16836,7 @@
     </row>
     <row r="20" spans="3:4">
       <c r="C20" s="116" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D20">
         <v>9190</v>
@@ -16663,7 +16844,7 @@
     </row>
     <row r="21" spans="3:4">
       <c r="C21" s="116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21">
         <v>15540</v>
@@ -16679,7 +16860,7 @@
     </row>
     <row r="23" spans="3:4">
       <c r="C23" s="116" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23">
         <v>5900</v>
@@ -16687,7 +16868,7 @@
     </row>
     <row r="24" spans="3:4" ht="28.8">
       <c r="C24" s="116" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24">
         <v>10000</v>

--- a/Zen_Estate_Combined_Expenses_Q1.xlsx
+++ b/Zen_Estate_Combined_Expenses_Q1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 11 - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8856BE-1A56-4652-B3B1-14B3B59C43F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B7D9DF-8A37-4702-A459-614AA38048C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="201">
   <si>
     <t>Opening Balance = 11,52,000/-</t>
   </si>
@@ -625,6 +625,21 @@
   </si>
   <si>
     <t>Media Cleaning</t>
+  </si>
+  <si>
+    <t>100 Chairs</t>
+  </si>
+  <si>
+    <t>Wardrobe for office</t>
+  </si>
+  <si>
+    <t>garden Pipe for watering</t>
+  </si>
+  <si>
+    <t>Club house panel lights</t>
+  </si>
+  <si>
+    <t>100 mtr Polycab wire</t>
   </si>
 </sst>
 </file>
@@ -1550,6 +1565,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1557,12 +1578,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1931,28 +1946,28 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
@@ -3103,28 +3118,28 @@
       </c>
     </row>
     <row r="21" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="119"/>
-      <c r="S21" s="119"/>
-      <c r="T21" s="119"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="121"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -4226,28 +4241,28 @@
       </c>
     </row>
     <row r="37" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A37" s="119" t="s">
+      <c r="A37" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="119"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="119"/>
-      <c r="L37" s="119"/>
-      <c r="M37" s="119"/>
-      <c r="N37" s="119"/>
-      <c r="O37" s="119"/>
-      <c r="P37" s="119"/>
-      <c r="Q37" s="119"/>
-      <c r="R37" s="119"/>
-      <c r="S37" s="119"/>
-      <c r="T37" s="119"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="121"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
@@ -4257,23 +4272,23 @@
       <c r="AA37" s="34"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="34"/>
-      <c r="AE37" s="117" t="s">
+      <c r="AE37" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF37" s="118"/>
-      <c r="AG37" s="118"/>
-      <c r="AH37" s="118"/>
-      <c r="AI37" s="118"/>
-      <c r="AJ37" s="118"/>
-      <c r="AK37" s="118"/>
-      <c r="AL37" s="118"/>
-      <c r="AM37" s="118"/>
-      <c r="AN37" s="118"/>
-      <c r="AO37" s="118"/>
-      <c r="AP37" s="118"/>
-      <c r="AQ37" s="118"/>
-      <c r="AR37" s="118"/>
-      <c r="AS37" s="118"/>
+      <c r="AF37" s="120"/>
+      <c r="AG37" s="120"/>
+      <c r="AH37" s="120"/>
+      <c r="AI37" s="120"/>
+      <c r="AJ37" s="120"/>
+      <c r="AK37" s="120"/>
+      <c r="AL37" s="120"/>
+      <c r="AM37" s="120"/>
+      <c r="AN37" s="120"/>
+      <c r="AO37" s="120"/>
+      <c r="AP37" s="120"/>
+      <c r="AQ37" s="120"/>
+      <c r="AR37" s="120"/>
+      <c r="AS37" s="120"/>
     </row>
     <row r="38" spans="1:46" ht="15" thickBot="1">
       <c r="A38" s="11" t="s">
@@ -5394,51 +5409,51 @@
       </c>
     </row>
     <row r="54" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A54" s="119" t="s">
+      <c r="A54" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="119"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="119"/>
-      <c r="K54" s="119"/>
-      <c r="L54" s="119"/>
-      <c r="M54" s="119"/>
-      <c r="N54" s="119"/>
-      <c r="O54" s="119"/>
-      <c r="P54" s="119"/>
-      <c r="Q54" s="119"/>
-      <c r="R54" s="119"/>
-      <c r="S54" s="119"/>
-      <c r="T54" s="119"/>
+      <c r="B54" s="121"/>
+      <c r="C54" s="121"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="121"/>
+      <c r="I54" s="121"/>
+      <c r="J54" s="121"/>
+      <c r="K54" s="121"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="121"/>
+      <c r="R54" s="121"/>
+      <c r="S54" s="121"/>
+      <c r="T54" s="121"/>
       <c r="U54" s="10"/>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
       <c r="X54" s="82"/>
       <c r="Y54" s="82"/>
       <c r="Z54" s="83"/>
-      <c r="AE54" s="117" t="s">
+      <c r="AE54" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF54" s="118"/>
-      <c r="AG54" s="118"/>
-      <c r="AH54" s="118"/>
-      <c r="AI54" s="118"/>
-      <c r="AJ54" s="118"/>
-      <c r="AK54" s="118"/>
-      <c r="AL54" s="118"/>
-      <c r="AM54" s="118"/>
-      <c r="AN54" s="118"/>
-      <c r="AO54" s="118"/>
-      <c r="AP54" s="118"/>
-      <c r="AQ54" s="118"/>
-      <c r="AR54" s="118"/>
-      <c r="AS54" s="118"/>
+      <c r="AF54" s="120"/>
+      <c r="AG54" s="120"/>
+      <c r="AH54" s="120"/>
+      <c r="AI54" s="120"/>
+      <c r="AJ54" s="120"/>
+      <c r="AK54" s="120"/>
+      <c r="AL54" s="120"/>
+      <c r="AM54" s="120"/>
+      <c r="AN54" s="120"/>
+      <c r="AO54" s="120"/>
+      <c r="AP54" s="120"/>
+      <c r="AQ54" s="120"/>
+      <c r="AR54" s="120"/>
+      <c r="AS54" s="120"/>
     </row>
     <row r="55" spans="1:46" ht="15" thickBot="1">
       <c r="A55" s="11" t="s">
@@ -6512,54 +6527,54 @@
       <c r="V68" s="20"/>
     </row>
     <row r="69" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A69" s="119" t="s">
+      <c r="A69" s="121" t="s">
         <v>104</v>
       </c>
-      <c r="B69" s="119"/>
-      <c r="C69" s="119"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="119"/>
-      <c r="H69" s="119"/>
-      <c r="I69" s="119"/>
-      <c r="J69" s="119"/>
-      <c r="K69" s="119"/>
-      <c r="L69" s="119"/>
-      <c r="M69" s="119"/>
-      <c r="N69" s="119"/>
-      <c r="O69" s="119"/>
-      <c r="P69" s="119"/>
-      <c r="Q69" s="119"/>
-      <c r="R69" s="119"/>
-      <c r="S69" s="119"/>
-      <c r="T69" s="119"/>
+      <c r="B69" s="121"/>
+      <c r="C69" s="121"/>
+      <c r="D69" s="121"/>
+      <c r="E69" s="121"/>
+      <c r="F69" s="121"/>
+      <c r="G69" s="121"/>
+      <c r="H69" s="121"/>
+      <c r="I69" s="121"/>
+      <c r="J69" s="121"/>
+      <c r="K69" s="121"/>
+      <c r="L69" s="121"/>
+      <c r="M69" s="121"/>
+      <c r="N69" s="121"/>
+      <c r="O69" s="121"/>
+      <c r="P69" s="121"/>
+      <c r="Q69" s="121"/>
+      <c r="R69" s="121"/>
+      <c r="S69" s="121"/>
+      <c r="T69" s="121"/>
       <c r="U69" s="10"/>
       <c r="V69" s="10"/>
       <c r="W69" s="10"/>
       <c r="X69" s="10"/>
       <c r="Y69" s="10"/>
       <c r="Z69" s="10"/>
-      <c r="AA69" s="120"/>
-      <c r="AB69" s="121"/>
+      <c r="AA69" s="117"/>
+      <c r="AB69" s="118"/>
       <c r="AC69" s="103"/>
-      <c r="AE69" s="117" t="s">
+      <c r="AE69" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF69" s="118"/>
-      <c r="AG69" s="118"/>
-      <c r="AH69" s="118"/>
-      <c r="AI69" s="118"/>
-      <c r="AJ69" s="118"/>
-      <c r="AK69" s="118"/>
-      <c r="AL69" s="118"/>
-      <c r="AM69" s="118"/>
-      <c r="AN69" s="118"/>
-      <c r="AO69" s="118"/>
-      <c r="AP69" s="118"/>
-      <c r="AQ69" s="118"/>
-      <c r="AR69" s="118"/>
-      <c r="AS69" s="118"/>
+      <c r="AF69" s="120"/>
+      <c r="AG69" s="120"/>
+      <c r="AH69" s="120"/>
+      <c r="AI69" s="120"/>
+      <c r="AJ69" s="120"/>
+      <c r="AK69" s="120"/>
+      <c r="AL69" s="120"/>
+      <c r="AM69" s="120"/>
+      <c r="AN69" s="120"/>
+      <c r="AO69" s="120"/>
+      <c r="AP69" s="120"/>
+      <c r="AQ69" s="120"/>
+      <c r="AR69" s="120"/>
+      <c r="AS69" s="120"/>
     </row>
     <row r="70" spans="1:45" ht="43.8" thickBot="1">
       <c r="A70" s="11" t="s">
@@ -7683,54 +7698,54 @@
       </c>
     </row>
     <row r="87" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A87" s="119" t="s">
+      <c r="A87" s="121" t="s">
         <v>109</v>
       </c>
-      <c r="B87" s="119"/>
-      <c r="C87" s="119"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="119"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="119"/>
-      <c r="H87" s="119"/>
-      <c r="I87" s="119"/>
-      <c r="J87" s="119"/>
-      <c r="K87" s="119"/>
-      <c r="L87" s="119"/>
-      <c r="M87" s="119"/>
-      <c r="N87" s="119"/>
-      <c r="O87" s="119"/>
-      <c r="P87" s="119"/>
-      <c r="Q87" s="119"/>
-      <c r="R87" s="119"/>
-      <c r="S87" s="119"/>
-      <c r="T87" s="119"/>
+      <c r="B87" s="121"/>
+      <c r="C87" s="121"/>
+      <c r="D87" s="121"/>
+      <c r="E87" s="121"/>
+      <c r="F87" s="121"/>
+      <c r="G87" s="121"/>
+      <c r="H87" s="121"/>
+      <c r="I87" s="121"/>
+      <c r="J87" s="121"/>
+      <c r="K87" s="121"/>
+      <c r="L87" s="121"/>
+      <c r="M87" s="121"/>
+      <c r="N87" s="121"/>
+      <c r="O87" s="121"/>
+      <c r="P87" s="121"/>
+      <c r="Q87" s="121"/>
+      <c r="R87" s="121"/>
+      <c r="S87" s="121"/>
+      <c r="T87" s="121"/>
       <c r="U87" s="10"/>
       <c r="V87" s="10"/>
       <c r="W87" s="10"/>
       <c r="X87" s="10"/>
       <c r="Y87" s="10"/>
       <c r="Z87" s="10"/>
-      <c r="AA87" s="120"/>
-      <c r="AB87" s="121"/>
+      <c r="AA87" s="117"/>
+      <c r="AB87" s="118"/>
       <c r="AC87" s="103"/>
-      <c r="AE87" s="117" t="s">
+      <c r="AE87" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF87" s="118"/>
-      <c r="AG87" s="118"/>
-      <c r="AH87" s="118"/>
-      <c r="AI87" s="118"/>
-      <c r="AJ87" s="118"/>
-      <c r="AK87" s="118"/>
-      <c r="AL87" s="118"/>
-      <c r="AM87" s="118"/>
-      <c r="AN87" s="118"/>
-      <c r="AO87" s="118"/>
-      <c r="AP87" s="118"/>
-      <c r="AQ87" s="118"/>
-      <c r="AR87" s="118"/>
-      <c r="AS87" s="118"/>
+      <c r="AF87" s="120"/>
+      <c r="AG87" s="120"/>
+      <c r="AH87" s="120"/>
+      <c r="AI87" s="120"/>
+      <c r="AJ87" s="120"/>
+      <c r="AK87" s="120"/>
+      <c r="AL87" s="120"/>
+      <c r="AM87" s="120"/>
+      <c r="AN87" s="120"/>
+      <c r="AO87" s="120"/>
+      <c r="AP87" s="120"/>
+      <c r="AQ87" s="120"/>
+      <c r="AR87" s="120"/>
+      <c r="AS87" s="120"/>
     </row>
     <row r="88" spans="1:46" ht="43.8" thickBot="1">
       <c r="A88" s="11" t="s">
@@ -8873,54 +8888,54 @@
       </c>
     </row>
     <row r="103" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A103" s="119" t="s">
+      <c r="A103" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="B103" s="119"/>
-      <c r="C103" s="119"/>
-      <c r="D103" s="119"/>
-      <c r="E103" s="119"/>
-      <c r="F103" s="119"/>
-      <c r="G103" s="119"/>
-      <c r="H103" s="119"/>
-      <c r="I103" s="119"/>
-      <c r="J103" s="119"/>
-      <c r="K103" s="119"/>
-      <c r="L103" s="119"/>
-      <c r="M103" s="119"/>
-      <c r="N103" s="119"/>
-      <c r="O103" s="119"/>
-      <c r="P103" s="119"/>
-      <c r="Q103" s="119"/>
-      <c r="R103" s="119"/>
-      <c r="S103" s="119"/>
-      <c r="T103" s="119"/>
+      <c r="B103" s="121"/>
+      <c r="C103" s="121"/>
+      <c r="D103" s="121"/>
+      <c r="E103" s="121"/>
+      <c r="F103" s="121"/>
+      <c r="G103" s="121"/>
+      <c r="H103" s="121"/>
+      <c r="I103" s="121"/>
+      <c r="J103" s="121"/>
+      <c r="K103" s="121"/>
+      <c r="L103" s="121"/>
+      <c r="M103" s="121"/>
+      <c r="N103" s="121"/>
+      <c r="O103" s="121"/>
+      <c r="P103" s="121"/>
+      <c r="Q103" s="121"/>
+      <c r="R103" s="121"/>
+      <c r="S103" s="121"/>
+      <c r="T103" s="121"/>
       <c r="U103" s="10"/>
       <c r="V103" s="10"/>
       <c r="W103" s="10"/>
       <c r="X103" s="10"/>
       <c r="Y103" s="10"/>
       <c r="Z103" s="10"/>
-      <c r="AA103" s="120"/>
-      <c r="AB103" s="121"/>
+      <c r="AA103" s="117"/>
+      <c r="AB103" s="118"/>
       <c r="AC103" s="103"/>
-      <c r="AE103" s="117" t="s">
+      <c r="AE103" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF103" s="118"/>
-      <c r="AG103" s="118"/>
-      <c r="AH103" s="118"/>
-      <c r="AI103" s="118"/>
-      <c r="AJ103" s="118"/>
-      <c r="AK103" s="118"/>
-      <c r="AL103" s="118"/>
-      <c r="AM103" s="118"/>
-      <c r="AN103" s="118"/>
-      <c r="AO103" s="118"/>
-      <c r="AP103" s="118"/>
-      <c r="AQ103" s="118"/>
-      <c r="AR103" s="118"/>
-      <c r="AS103" s="118"/>
+      <c r="AF103" s="120"/>
+      <c r="AG103" s="120"/>
+      <c r="AH103" s="120"/>
+      <c r="AI103" s="120"/>
+      <c r="AJ103" s="120"/>
+      <c r="AK103" s="120"/>
+      <c r="AL103" s="120"/>
+      <c r="AM103" s="120"/>
+      <c r="AN103" s="120"/>
+      <c r="AO103" s="120"/>
+      <c r="AP103" s="120"/>
+      <c r="AQ103" s="120"/>
+      <c r="AR103" s="120"/>
+      <c r="AS103" s="120"/>
     </row>
     <row r="104" spans="1:45" ht="43.8" thickBot="1">
       <c r="A104" s="11" t="s">
@@ -10067,54 +10082,54 @@
       </c>
     </row>
     <row r="120" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A120" s="119" t="s">
+      <c r="A120" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="B120" s="119"/>
-      <c r="C120" s="119"/>
-      <c r="D120" s="119"/>
-      <c r="E120" s="119"/>
-      <c r="F120" s="119"/>
-      <c r="G120" s="119"/>
-      <c r="H120" s="119"/>
-      <c r="I120" s="119"/>
-      <c r="J120" s="119"/>
-      <c r="K120" s="119"/>
-      <c r="L120" s="119"/>
-      <c r="M120" s="119"/>
-      <c r="N120" s="119"/>
-      <c r="O120" s="119"/>
-      <c r="P120" s="119"/>
-      <c r="Q120" s="119"/>
-      <c r="R120" s="119"/>
-      <c r="S120" s="119"/>
-      <c r="T120" s="119"/>
+      <c r="B120" s="121"/>
+      <c r="C120" s="121"/>
+      <c r="D120" s="121"/>
+      <c r="E120" s="121"/>
+      <c r="F120" s="121"/>
+      <c r="G120" s="121"/>
+      <c r="H120" s="121"/>
+      <c r="I120" s="121"/>
+      <c r="J120" s="121"/>
+      <c r="K120" s="121"/>
+      <c r="L120" s="121"/>
+      <c r="M120" s="121"/>
+      <c r="N120" s="121"/>
+      <c r="O120" s="121"/>
+      <c r="P120" s="121"/>
+      <c r="Q120" s="121"/>
+      <c r="R120" s="121"/>
+      <c r="S120" s="121"/>
+      <c r="T120" s="121"/>
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
       <c r="W120" s="10"/>
       <c r="X120" s="10"/>
       <c r="Y120" s="10"/>
       <c r="Z120" s="10"/>
-      <c r="AA120" s="120"/>
-      <c r="AB120" s="121"/>
+      <c r="AA120" s="117"/>
+      <c r="AB120" s="118"/>
       <c r="AC120" s="103"/>
-      <c r="AE120" s="117" t="s">
+      <c r="AE120" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF120" s="118"/>
-      <c r="AG120" s="118"/>
-      <c r="AH120" s="118"/>
-      <c r="AI120" s="118"/>
-      <c r="AJ120" s="118"/>
-      <c r="AK120" s="118"/>
-      <c r="AL120" s="118"/>
-      <c r="AM120" s="118"/>
-      <c r="AN120" s="118"/>
-      <c r="AO120" s="118"/>
-      <c r="AP120" s="118"/>
-      <c r="AQ120" s="118"/>
-      <c r="AR120" s="118"/>
-      <c r="AS120" s="118"/>
+      <c r="AF120" s="120"/>
+      <c r="AG120" s="120"/>
+      <c r="AH120" s="120"/>
+      <c r="AI120" s="120"/>
+      <c r="AJ120" s="120"/>
+      <c r="AK120" s="120"/>
+      <c r="AL120" s="120"/>
+      <c r="AM120" s="120"/>
+      <c r="AN120" s="120"/>
+      <c r="AO120" s="120"/>
+      <c r="AP120" s="120"/>
+      <c r="AQ120" s="120"/>
+      <c r="AR120" s="120"/>
+      <c r="AS120" s="120"/>
     </row>
     <row r="121" spans="1:45" ht="43.8" thickBot="1">
       <c r="A121" s="11" t="s">
@@ -11306,54 +11321,54 @@
       <c r="E138" s="110"/>
     </row>
     <row r="139" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A139" s="119" t="s">
+      <c r="A139" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="B139" s="119"/>
-      <c r="C139" s="119"/>
-      <c r="D139" s="119"/>
-      <c r="E139" s="119"/>
-      <c r="F139" s="119"/>
-      <c r="G139" s="119"/>
-      <c r="H139" s="119"/>
-      <c r="I139" s="119"/>
-      <c r="J139" s="119"/>
-      <c r="K139" s="119"/>
-      <c r="L139" s="119"/>
-      <c r="M139" s="119"/>
-      <c r="N139" s="119"/>
-      <c r="O139" s="119"/>
-      <c r="P139" s="119"/>
-      <c r="Q139" s="119"/>
-      <c r="R139" s="119"/>
-      <c r="S139" s="119"/>
-      <c r="T139" s="119"/>
+      <c r="B139" s="121"/>
+      <c r="C139" s="121"/>
+      <c r="D139" s="121"/>
+      <c r="E139" s="121"/>
+      <c r="F139" s="121"/>
+      <c r="G139" s="121"/>
+      <c r="H139" s="121"/>
+      <c r="I139" s="121"/>
+      <c r="J139" s="121"/>
+      <c r="K139" s="121"/>
+      <c r="L139" s="121"/>
+      <c r="M139" s="121"/>
+      <c r="N139" s="121"/>
+      <c r="O139" s="121"/>
+      <c r="P139" s="121"/>
+      <c r="Q139" s="121"/>
+      <c r="R139" s="121"/>
+      <c r="S139" s="121"/>
+      <c r="T139" s="121"/>
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
       <c r="W139" s="10"/>
       <c r="X139" s="10"/>
       <c r="Y139" s="10"/>
       <c r="Z139" s="10"/>
-      <c r="AA139" s="120"/>
-      <c r="AB139" s="121"/>
+      <c r="AA139" s="117"/>
+      <c r="AB139" s="118"/>
       <c r="AC139" s="103"/>
-      <c r="AE139" s="117" t="s">
+      <c r="AE139" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF139" s="118"/>
-      <c r="AG139" s="118"/>
-      <c r="AH139" s="118"/>
-      <c r="AI139" s="118"/>
-      <c r="AJ139" s="118"/>
-      <c r="AK139" s="118"/>
-      <c r="AL139" s="118"/>
-      <c r="AM139" s="118"/>
-      <c r="AN139" s="118"/>
-      <c r="AO139" s="118"/>
-      <c r="AP139" s="118"/>
-      <c r="AQ139" s="118"/>
-      <c r="AR139" s="118"/>
-      <c r="AS139" s="118"/>
+      <c r="AF139" s="120"/>
+      <c r="AG139" s="120"/>
+      <c r="AH139" s="120"/>
+      <c r="AI139" s="120"/>
+      <c r="AJ139" s="120"/>
+      <c r="AK139" s="120"/>
+      <c r="AL139" s="120"/>
+      <c r="AM139" s="120"/>
+      <c r="AN139" s="120"/>
+      <c r="AO139" s="120"/>
+      <c r="AP139" s="120"/>
+      <c r="AQ139" s="120"/>
+      <c r="AR139" s="120"/>
+      <c r="AS139" s="120"/>
     </row>
     <row r="140" spans="1:45" ht="43.8" thickBot="1">
       <c r="A140" s="11" t="s">
@@ -12541,54 +12556,54 @@
       </c>
     </row>
     <row r="158" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A158" s="119" t="s">
+      <c r="A158" s="121" t="s">
         <v>150</v>
       </c>
-      <c r="B158" s="119"/>
-      <c r="C158" s="119"/>
-      <c r="D158" s="119"/>
-      <c r="E158" s="119"/>
-      <c r="F158" s="119"/>
-      <c r="G158" s="119"/>
-      <c r="H158" s="119"/>
-      <c r="I158" s="119"/>
-      <c r="J158" s="119"/>
-      <c r="K158" s="119"/>
-      <c r="L158" s="119"/>
-      <c r="M158" s="119"/>
-      <c r="N158" s="119"/>
-      <c r="O158" s="119"/>
-      <c r="P158" s="119"/>
-      <c r="Q158" s="119"/>
-      <c r="R158" s="119"/>
-      <c r="S158" s="119"/>
-      <c r="T158" s="119"/>
+      <c r="B158" s="121"/>
+      <c r="C158" s="121"/>
+      <c r="D158" s="121"/>
+      <c r="E158" s="121"/>
+      <c r="F158" s="121"/>
+      <c r="G158" s="121"/>
+      <c r="H158" s="121"/>
+      <c r="I158" s="121"/>
+      <c r="J158" s="121"/>
+      <c r="K158" s="121"/>
+      <c r="L158" s="121"/>
+      <c r="M158" s="121"/>
+      <c r="N158" s="121"/>
+      <c r="O158" s="121"/>
+      <c r="P158" s="121"/>
+      <c r="Q158" s="121"/>
+      <c r="R158" s="121"/>
+      <c r="S158" s="121"/>
+      <c r="T158" s="121"/>
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
       <c r="W158" s="10"/>
       <c r="X158" s="10"/>
       <c r="Y158" s="10"/>
       <c r="Z158" s="10"/>
-      <c r="AA158" s="120"/>
-      <c r="AB158" s="121"/>
+      <c r="AA158" s="117"/>
+      <c r="AB158" s="118"/>
       <c r="AC158" s="103"/>
-      <c r="AE158" s="117" t="s">
+      <c r="AE158" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF158" s="118"/>
-      <c r="AG158" s="118"/>
-      <c r="AH158" s="118"/>
-      <c r="AI158" s="118"/>
-      <c r="AJ158" s="118"/>
-      <c r="AK158" s="118"/>
-      <c r="AL158" s="118"/>
-      <c r="AM158" s="118"/>
-      <c r="AN158" s="118"/>
-      <c r="AO158" s="118"/>
-      <c r="AP158" s="118"/>
-      <c r="AQ158" s="118"/>
-      <c r="AR158" s="118"/>
-      <c r="AS158" s="118"/>
+      <c r="AF158" s="120"/>
+      <c r="AG158" s="120"/>
+      <c r="AH158" s="120"/>
+      <c r="AI158" s="120"/>
+      <c r="AJ158" s="120"/>
+      <c r="AK158" s="120"/>
+      <c r="AL158" s="120"/>
+      <c r="AM158" s="120"/>
+      <c r="AN158" s="120"/>
+      <c r="AO158" s="120"/>
+      <c r="AP158" s="120"/>
+      <c r="AQ158" s="120"/>
+      <c r="AR158" s="120"/>
+      <c r="AS158" s="120"/>
     </row>
     <row r="159" spans="1:45" ht="43.8" thickBot="1">
       <c r="A159" s="11" t="s">
@@ -13737,54 +13752,54 @@
       </c>
     </row>
     <row r="174" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A174" s="119" t="s">
+      <c r="A174" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="B174" s="119"/>
-      <c r="C174" s="119"/>
-      <c r="D174" s="119"/>
-      <c r="E174" s="119"/>
-      <c r="F174" s="119"/>
-      <c r="G174" s="119"/>
-      <c r="H174" s="119"/>
-      <c r="I174" s="119"/>
-      <c r="J174" s="119"/>
-      <c r="K174" s="119"/>
-      <c r="L174" s="119"/>
-      <c r="M174" s="119"/>
-      <c r="N174" s="119"/>
-      <c r="O174" s="119"/>
-      <c r="P174" s="119"/>
-      <c r="Q174" s="119"/>
-      <c r="R174" s="119"/>
-      <c r="S174" s="119"/>
-      <c r="T174" s="119"/>
+      <c r="B174" s="121"/>
+      <c r="C174" s="121"/>
+      <c r="D174" s="121"/>
+      <c r="E174" s="121"/>
+      <c r="F174" s="121"/>
+      <c r="G174" s="121"/>
+      <c r="H174" s="121"/>
+      <c r="I174" s="121"/>
+      <c r="J174" s="121"/>
+      <c r="K174" s="121"/>
+      <c r="L174" s="121"/>
+      <c r="M174" s="121"/>
+      <c r="N174" s="121"/>
+      <c r="O174" s="121"/>
+      <c r="P174" s="121"/>
+      <c r="Q174" s="121"/>
+      <c r="R174" s="121"/>
+      <c r="S174" s="121"/>
+      <c r="T174" s="121"/>
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
       <c r="W174" s="10"/>
       <c r="X174" s="10"/>
       <c r="Y174" s="10"/>
       <c r="Z174" s="10"/>
-      <c r="AA174" s="120"/>
-      <c r="AB174" s="121"/>
+      <c r="AA174" s="117"/>
+      <c r="AB174" s="118"/>
       <c r="AC174" s="103"/>
-      <c r="AE174" s="117" t="s">
+      <c r="AE174" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF174" s="118"/>
-      <c r="AG174" s="118"/>
-      <c r="AH174" s="118"/>
-      <c r="AI174" s="118"/>
-      <c r="AJ174" s="118"/>
-      <c r="AK174" s="118"/>
-      <c r="AL174" s="118"/>
-      <c r="AM174" s="118"/>
-      <c r="AN174" s="118"/>
-      <c r="AO174" s="118"/>
-      <c r="AP174" s="118"/>
-      <c r="AQ174" s="118"/>
-      <c r="AR174" s="118"/>
-      <c r="AS174" s="118"/>
+      <c r="AF174" s="120"/>
+      <c r="AG174" s="120"/>
+      <c r="AH174" s="120"/>
+      <c r="AI174" s="120"/>
+      <c r="AJ174" s="120"/>
+      <c r="AK174" s="120"/>
+      <c r="AL174" s="120"/>
+      <c r="AM174" s="120"/>
+      <c r="AN174" s="120"/>
+      <c r="AO174" s="120"/>
+      <c r="AP174" s="120"/>
+      <c r="AQ174" s="120"/>
+      <c r="AR174" s="120"/>
+      <c r="AS174" s="120"/>
     </row>
     <row r="175" spans="1:45" ht="43.8" thickBot="1">
       <c r="A175" s="11" t="s">
@@ -14937,54 +14952,54 @@
       </c>
     </row>
     <row r="192" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A192" s="119" t="s">
+      <c r="A192" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="B192" s="119"/>
-      <c r="C192" s="119"/>
-      <c r="D192" s="119"/>
-      <c r="E192" s="119"/>
-      <c r="F192" s="119"/>
-      <c r="G192" s="119"/>
-      <c r="H192" s="119"/>
-      <c r="I192" s="119"/>
-      <c r="J192" s="119"/>
-      <c r="K192" s="119"/>
-      <c r="L192" s="119"/>
-      <c r="M192" s="119"/>
-      <c r="N192" s="119"/>
-      <c r="O192" s="119"/>
-      <c r="P192" s="119"/>
-      <c r="Q192" s="119"/>
-      <c r="R192" s="119"/>
-      <c r="S192" s="119"/>
-      <c r="T192" s="119"/>
+      <c r="B192" s="121"/>
+      <c r="C192" s="121"/>
+      <c r="D192" s="121"/>
+      <c r="E192" s="121"/>
+      <c r="F192" s="121"/>
+      <c r="G192" s="121"/>
+      <c r="H192" s="121"/>
+      <c r="I192" s="121"/>
+      <c r="J192" s="121"/>
+      <c r="K192" s="121"/>
+      <c r="L192" s="121"/>
+      <c r="M192" s="121"/>
+      <c r="N192" s="121"/>
+      <c r="O192" s="121"/>
+      <c r="P192" s="121"/>
+      <c r="Q192" s="121"/>
+      <c r="R192" s="121"/>
+      <c r="S192" s="121"/>
+      <c r="T192" s="121"/>
       <c r="U192" s="10"/>
       <c r="V192" s="10"/>
       <c r="W192" s="10"/>
       <c r="X192" s="10"/>
       <c r="Y192" s="10"/>
       <c r="Z192" s="10"/>
-      <c r="AA192" s="120"/>
-      <c r="AB192" s="121"/>
+      <c r="AA192" s="117"/>
+      <c r="AB192" s="118"/>
       <c r="AC192" s="103"/>
-      <c r="AE192" s="117" t="s">
+      <c r="AE192" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF192" s="118"/>
-      <c r="AG192" s="118"/>
-      <c r="AH192" s="118"/>
-      <c r="AI192" s="118"/>
-      <c r="AJ192" s="118"/>
-      <c r="AK192" s="118"/>
-      <c r="AL192" s="118"/>
-      <c r="AM192" s="118"/>
-      <c r="AN192" s="118"/>
-      <c r="AO192" s="118"/>
-      <c r="AP192" s="118"/>
-      <c r="AQ192" s="118"/>
-      <c r="AR192" s="118"/>
-      <c r="AS192" s="118"/>
+      <c r="AF192" s="120"/>
+      <c r="AG192" s="120"/>
+      <c r="AH192" s="120"/>
+      <c r="AI192" s="120"/>
+      <c r="AJ192" s="120"/>
+      <c r="AK192" s="120"/>
+      <c r="AL192" s="120"/>
+      <c r="AM192" s="120"/>
+      <c r="AN192" s="120"/>
+      <c r="AO192" s="120"/>
+      <c r="AP192" s="120"/>
+      <c r="AQ192" s="120"/>
+      <c r="AR192" s="120"/>
+      <c r="AS192" s="120"/>
     </row>
     <row r="193" spans="1:45" ht="43.8" thickBot="1">
       <c r="A193" s="11" t="s">
@@ -15874,7 +15889,21 @@
       <c r="Z203" s="113" t="s">
         <v>195</v>
       </c>
-      <c r="AC203" s="33"/>
+      <c r="AA203" s="113" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB203" s="113" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC203" s="113" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD203" s="113" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE203" s="113" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="204" spans="1:45">
       <c r="A204" s="25">
@@ -15952,7 +15981,21 @@
       <c r="Z204" s="111">
         <v>46280</v>
       </c>
-      <c r="AC204" s="34"/>
+      <c r="AA204" s="111">
+        <v>46280</v>
+      </c>
+      <c r="AB204" s="111">
+        <v>46280</v>
+      </c>
+      <c r="AC204" s="111">
+        <v>46280</v>
+      </c>
+      <c r="AD204" s="111">
+        <v>46280</v>
+      </c>
+      <c r="AE204" s="111">
+        <v>46280</v>
+      </c>
     </row>
     <row r="205" spans="1:45" ht="15" thickBot="1">
       <c r="A205" s="25">
@@ -16030,7 +16073,21 @@
       <c r="Z205" s="112">
         <v>6000</v>
       </c>
-      <c r="AC205" s="20"/>
+      <c r="AA205" s="112">
+        <v>43000</v>
+      </c>
+      <c r="AB205" s="112">
+        <v>3000</v>
+      </c>
+      <c r="AC205" s="112">
+        <v>12914</v>
+      </c>
+      <c r="AD205" s="112">
+        <v>1200</v>
+      </c>
+      <c r="AE205" s="112">
+        <v>3190</v>
+      </c>
     </row>
     <row r="206" spans="1:45" ht="43.8" thickBot="1">
       <c r="A206" s="25">
@@ -16056,22 +16113,22 @@
         <v>33</v>
       </c>
       <c r="J206" s="60">
-        <f>SUM(G200:V200)-AE204</f>
-        <v>1726897.6999999997</v>
+        <f>SUM(G200:V200)-AD204</f>
+        <v>1680617.6999999997</v>
       </c>
       <c r="L206" s="67" t="s">
         <v>77</v>
       </c>
       <c r="M206" s="68">
         <f>(G206-J206)</f>
-        <v>212179.16000000061</v>
+        <v>258459.16000000061</v>
       </c>
       <c r="O206" s="61" t="s">
         <v>95</v>
       </c>
       <c r="P206" s="62">
-        <f>SUM(G205:Z205)</f>
-        <v>2046199</v>
+        <f>SUM(G205:AE205)</f>
+        <v>2109503</v>
       </c>
       <c r="Q206" s="20"/>
       <c r="R206" s="63" t="s">
@@ -16122,34 +16179,42 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="AA192:AB192"/>
-    <mergeCell ref="AE192:AS192"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="E192:H192"/>
-    <mergeCell ref="I192:L192"/>
-    <mergeCell ref="M192:P192"/>
-    <mergeCell ref="Q192:T192"/>
-    <mergeCell ref="AA174:AB174"/>
-    <mergeCell ref="AE174:AS174"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="E174:H174"/>
-    <mergeCell ref="I174:L174"/>
-    <mergeCell ref="M174:P174"/>
-    <mergeCell ref="Q174:T174"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="A158:D158"/>
-    <mergeCell ref="AE158:AS158"/>
-    <mergeCell ref="AA158:AB158"/>
-    <mergeCell ref="Q158:T158"/>
-    <mergeCell ref="M158:P158"/>
-    <mergeCell ref="I158:L158"/>
-    <mergeCell ref="AA139:AB139"/>
-    <mergeCell ref="AE139:AS139"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="M139:P139"/>
-    <mergeCell ref="Q139:T139"/>
+    <mergeCell ref="AE103:AS103"/>
+    <mergeCell ref="AE120:AS120"/>
+    <mergeCell ref="AE37:AS37"/>
+    <mergeCell ref="AE54:AS54"/>
+    <mergeCell ref="AE69:AS69"/>
+    <mergeCell ref="AE87:AS87"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="M103:P103"/>
+    <mergeCell ref="Q103:T103"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q54:T54"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="M87:P87"/>
+    <mergeCell ref="Q87:T87"/>
     <mergeCell ref="AA120:AB120"/>
     <mergeCell ref="AE2:AS2"/>
     <mergeCell ref="AE21:AS21"/>
@@ -16166,42 +16231,34 @@
     <mergeCell ref="I69:L69"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="M87:P87"/>
-    <mergeCell ref="Q87:T87"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q54:T54"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="M103:P103"/>
-    <mergeCell ref="Q103:T103"/>
-    <mergeCell ref="AE103:AS103"/>
-    <mergeCell ref="AE120:AS120"/>
-    <mergeCell ref="AE37:AS37"/>
-    <mergeCell ref="AE54:AS54"/>
-    <mergeCell ref="AE69:AS69"/>
-    <mergeCell ref="AE87:AS87"/>
+    <mergeCell ref="AA139:AB139"/>
+    <mergeCell ref="AE139:AS139"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="M139:P139"/>
+    <mergeCell ref="Q139:T139"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="AE158:AS158"/>
+    <mergeCell ref="AA158:AB158"/>
+    <mergeCell ref="Q158:T158"/>
+    <mergeCell ref="M158:P158"/>
+    <mergeCell ref="I158:L158"/>
+    <mergeCell ref="AA174:AB174"/>
+    <mergeCell ref="AE174:AS174"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="E174:H174"/>
+    <mergeCell ref="I174:L174"/>
+    <mergeCell ref="M174:P174"/>
+    <mergeCell ref="Q174:T174"/>
+    <mergeCell ref="AA192:AB192"/>
+    <mergeCell ref="AE192:AS192"/>
+    <mergeCell ref="A192:D192"/>
+    <mergeCell ref="E192:H192"/>
+    <mergeCell ref="I192:L192"/>
+    <mergeCell ref="M192:P192"/>
+    <mergeCell ref="Q192:T192"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16683,7 +16740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F2BD5F-5FC8-4604-BC5A-7F98636B3F60}">
-  <dimension ref="C2:D24"/>
+  <dimension ref="C2:D32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.5546875" customWidth="1"/>
@@ -16872,6 +16929,70 @@
       </c>
       <c r="D24">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="116" t="s">
+        <v>193</v>
+      </c>
+      <c r="D25">
+        <v>28260</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="116" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="116" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30">
+        <v>12914</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="116" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32">
+        <v>3190</v>
       </c>
     </row>
   </sheetData>

--- a/Zen_Estate_Combined_Expenses_Q1.xlsx
+++ b/Zen_Estate_Combined_Expenses_Q1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 11 - Copy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B7D9DF-8A37-4702-A459-614AA38048C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1065D89E-D6D8-4C79-A1E8-A2DEE0AABE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="204">
   <si>
     <t>Opening Balance = 11,52,000/-</t>
   </si>
@@ -597,9 +597,6 @@
     <t>Gym Glass Door Granite Replacemnt</t>
   </si>
   <si>
-    <t>FD</t>
-  </si>
-  <si>
     <t>Diesel Re-filling</t>
   </si>
   <si>
@@ -640,6 +637,18 @@
   </si>
   <si>
     <t>100 mtr Polycab wire</t>
+  </si>
+  <si>
+    <t>DG Servicing</t>
+  </si>
+  <si>
+    <t>Repair Bypass Pump</t>
+  </si>
+  <si>
+    <t>Pipeline Bracket work in B1</t>
+  </si>
+  <si>
+    <t>Fire AMC</t>
   </si>
 </sst>
 </file>
@@ -1565,12 +1574,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1578,6 +1581,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1946,28 +1955,28 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
@@ -3118,28 +3127,28 @@
       </c>
     </row>
     <row r="21" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A21" s="121" t="s">
+      <c r="A21" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="121"/>
-      <c r="S21" s="121"/>
-      <c r="T21" s="121"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="119"/>
+      <c r="R21" s="119"/>
+      <c r="S21" s="119"/>
+      <c r="T21" s="119"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -4241,28 +4250,28 @@
       </c>
     </row>
     <row r="37" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A37" s="121" t="s">
+      <c r="A37" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="121"/>
-      <c r="C37" s="121"/>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="121"/>
-      <c r="K37" s="121"/>
-      <c r="L37" s="121"/>
-      <c r="M37" s="121"/>
-      <c r="N37" s="121"/>
-      <c r="O37" s="121"/>
-      <c r="P37" s="121"/>
-      <c r="Q37" s="121"/>
-      <c r="R37" s="121"/>
-      <c r="S37" s="121"/>
-      <c r="T37" s="121"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
+      <c r="H37" s="119"/>
+      <c r="I37" s="119"/>
+      <c r="J37" s="119"/>
+      <c r="K37" s="119"/>
+      <c r="L37" s="119"/>
+      <c r="M37" s="119"/>
+      <c r="N37" s="119"/>
+      <c r="O37" s="119"/>
+      <c r="P37" s="119"/>
+      <c r="Q37" s="119"/>
+      <c r="R37" s="119"/>
+      <c r="S37" s="119"/>
+      <c r="T37" s="119"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
@@ -4272,23 +4281,23 @@
       <c r="AA37" s="34"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="34"/>
-      <c r="AE37" s="119" t="s">
+      <c r="AE37" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF37" s="120"/>
-      <c r="AG37" s="120"/>
-      <c r="AH37" s="120"/>
-      <c r="AI37" s="120"/>
-      <c r="AJ37" s="120"/>
-      <c r="AK37" s="120"/>
-      <c r="AL37" s="120"/>
-      <c r="AM37" s="120"/>
-      <c r="AN37" s="120"/>
-      <c r="AO37" s="120"/>
-      <c r="AP37" s="120"/>
-      <c r="AQ37" s="120"/>
-      <c r="AR37" s="120"/>
-      <c r="AS37" s="120"/>
+      <c r="AF37" s="118"/>
+      <c r="AG37" s="118"/>
+      <c r="AH37" s="118"/>
+      <c r="AI37" s="118"/>
+      <c r="AJ37" s="118"/>
+      <c r="AK37" s="118"/>
+      <c r="AL37" s="118"/>
+      <c r="AM37" s="118"/>
+      <c r="AN37" s="118"/>
+      <c r="AO37" s="118"/>
+      <c r="AP37" s="118"/>
+      <c r="AQ37" s="118"/>
+      <c r="AR37" s="118"/>
+      <c r="AS37" s="118"/>
     </row>
     <row r="38" spans="1:46" ht="15" thickBot="1">
       <c r="A38" s="11" t="s">
@@ -5409,51 +5418,51 @@
       </c>
     </row>
     <row r="54" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A54" s="121" t="s">
+      <c r="A54" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="121"/>
-      <c r="C54" s="121"/>
-      <c r="D54" s="121"/>
-      <c r="E54" s="121"/>
-      <c r="F54" s="121"/>
-      <c r="G54" s="121"/>
-      <c r="H54" s="121"/>
-      <c r="I54" s="121"/>
-      <c r="J54" s="121"/>
-      <c r="K54" s="121"/>
-      <c r="L54" s="121"/>
-      <c r="M54" s="121"/>
-      <c r="N54" s="121"/>
-      <c r="O54" s="121"/>
-      <c r="P54" s="121"/>
-      <c r="Q54" s="121"/>
-      <c r="R54" s="121"/>
-      <c r="S54" s="121"/>
-      <c r="T54" s="121"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="119"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="119"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="119"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="119"/>
+      <c r="K54" s="119"/>
+      <c r="L54" s="119"/>
+      <c r="M54" s="119"/>
+      <c r="N54" s="119"/>
+      <c r="O54" s="119"/>
+      <c r="P54" s="119"/>
+      <c r="Q54" s="119"/>
+      <c r="R54" s="119"/>
+      <c r="S54" s="119"/>
+      <c r="T54" s="119"/>
       <c r="U54" s="10"/>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
       <c r="X54" s="82"/>
       <c r="Y54" s="82"/>
       <c r="Z54" s="83"/>
-      <c r="AE54" s="119" t="s">
+      <c r="AE54" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF54" s="120"/>
-      <c r="AG54" s="120"/>
-      <c r="AH54" s="120"/>
-      <c r="AI54" s="120"/>
-      <c r="AJ54" s="120"/>
-      <c r="AK54" s="120"/>
-      <c r="AL54" s="120"/>
-      <c r="AM54" s="120"/>
-      <c r="AN54" s="120"/>
-      <c r="AO54" s="120"/>
-      <c r="AP54" s="120"/>
-      <c r="AQ54" s="120"/>
-      <c r="AR54" s="120"/>
-      <c r="AS54" s="120"/>
+      <c r="AF54" s="118"/>
+      <c r="AG54" s="118"/>
+      <c r="AH54" s="118"/>
+      <c r="AI54" s="118"/>
+      <c r="AJ54" s="118"/>
+      <c r="AK54" s="118"/>
+      <c r="AL54" s="118"/>
+      <c r="AM54" s="118"/>
+      <c r="AN54" s="118"/>
+      <c r="AO54" s="118"/>
+      <c r="AP54" s="118"/>
+      <c r="AQ54" s="118"/>
+      <c r="AR54" s="118"/>
+      <c r="AS54" s="118"/>
     </row>
     <row r="55" spans="1:46" ht="15" thickBot="1">
       <c r="A55" s="11" t="s">
@@ -5717,9 +5726,11 @@
       </c>
       <c r="L57" s="14">
         <f>SUM(M57:N57)</f>
-        <v>405</v>
-      </c>
-      <c r="M57" s="14"/>
+        <v>25405</v>
+      </c>
+      <c r="M57" s="14">
+        <v>25000</v>
+      </c>
       <c r="N57" s="15">
         <v>405</v>
       </c>
@@ -6066,7 +6077,7 @@
       </c>
       <c r="L62" s="6">
         <f>SUM(L56:L61)</f>
-        <v>17808.68</v>
+        <v>42808.68</v>
       </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
@@ -6225,7 +6236,7 @@
       </c>
       <c r="L64" s="54">
         <f t="shared" ref="L64" si="39">(L63-L62)</f>
-        <v>1783.3199999999997</v>
+        <v>-23216.68</v>
       </c>
       <c r="M64" s="54"/>
       <c r="N64" s="54"/>
@@ -6498,14 +6509,14 @@
       </c>
       <c r="J68" s="60">
         <f>SUM(G62:V62)-AE66</f>
-        <v>1982383.1300000001</v>
+        <v>2007383.1300000001</v>
       </c>
       <c r="L68" s="67" t="s">
         <v>77</v>
       </c>
       <c r="M68" s="68">
         <f>(G68-J68)</f>
-        <v>16947.020000000019</v>
+        <v>-8052.9799999999814</v>
       </c>
       <c r="O68" s="61" t="s">
         <v>95</v>
@@ -6527,54 +6538,54 @@
       <c r="V68" s="20"/>
     </row>
     <row r="69" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A69" s="121" t="s">
+      <c r="A69" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="B69" s="121"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
-      <c r="E69" s="121"/>
-      <c r="F69" s="121"/>
-      <c r="G69" s="121"/>
-      <c r="H69" s="121"/>
-      <c r="I69" s="121"/>
-      <c r="J69" s="121"/>
-      <c r="K69" s="121"/>
-      <c r="L69" s="121"/>
-      <c r="M69" s="121"/>
-      <c r="N69" s="121"/>
-      <c r="O69" s="121"/>
-      <c r="P69" s="121"/>
-      <c r="Q69" s="121"/>
-      <c r="R69" s="121"/>
-      <c r="S69" s="121"/>
-      <c r="T69" s="121"/>
+      <c r="B69" s="119"/>
+      <c r="C69" s="119"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="119"/>
+      <c r="H69" s="119"/>
+      <c r="I69" s="119"/>
+      <c r="J69" s="119"/>
+      <c r="K69" s="119"/>
+      <c r="L69" s="119"/>
+      <c r="M69" s="119"/>
+      <c r="N69" s="119"/>
+      <c r="O69" s="119"/>
+      <c r="P69" s="119"/>
+      <c r="Q69" s="119"/>
+      <c r="R69" s="119"/>
+      <c r="S69" s="119"/>
+      <c r="T69" s="119"/>
       <c r="U69" s="10"/>
       <c r="V69" s="10"/>
       <c r="W69" s="10"/>
       <c r="X69" s="10"/>
       <c r="Y69" s="10"/>
       <c r="Z69" s="10"/>
-      <c r="AA69" s="117"/>
-      <c r="AB69" s="118"/>
+      <c r="AA69" s="120"/>
+      <c r="AB69" s="121"/>
       <c r="AC69" s="103"/>
-      <c r="AE69" s="119" t="s">
+      <c r="AE69" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF69" s="120"/>
-      <c r="AG69" s="120"/>
-      <c r="AH69" s="120"/>
-      <c r="AI69" s="120"/>
-      <c r="AJ69" s="120"/>
-      <c r="AK69" s="120"/>
-      <c r="AL69" s="120"/>
-      <c r="AM69" s="120"/>
-      <c r="AN69" s="120"/>
-      <c r="AO69" s="120"/>
-      <c r="AP69" s="120"/>
-      <c r="AQ69" s="120"/>
-      <c r="AR69" s="120"/>
-      <c r="AS69" s="120"/>
+      <c r="AF69" s="118"/>
+      <c r="AG69" s="118"/>
+      <c r="AH69" s="118"/>
+      <c r="AI69" s="118"/>
+      <c r="AJ69" s="118"/>
+      <c r="AK69" s="118"/>
+      <c r="AL69" s="118"/>
+      <c r="AM69" s="118"/>
+      <c r="AN69" s="118"/>
+      <c r="AO69" s="118"/>
+      <c r="AP69" s="118"/>
+      <c r="AQ69" s="118"/>
+      <c r="AR69" s="118"/>
+      <c r="AS69" s="118"/>
     </row>
     <row r="70" spans="1:45" ht="43.8" thickBot="1">
       <c r="A70" s="11" t="s">
@@ -7698,54 +7709,54 @@
       </c>
     </row>
     <row r="87" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A87" s="121" t="s">
+      <c r="A87" s="119" t="s">
         <v>109</v>
       </c>
-      <c r="B87" s="121"/>
-      <c r="C87" s="121"/>
-      <c r="D87" s="121"/>
-      <c r="E87" s="121"/>
-      <c r="F87" s="121"/>
-      <c r="G87" s="121"/>
-      <c r="H87" s="121"/>
-      <c r="I87" s="121"/>
-      <c r="J87" s="121"/>
-      <c r="K87" s="121"/>
-      <c r="L87" s="121"/>
-      <c r="M87" s="121"/>
-      <c r="N87" s="121"/>
-      <c r="O87" s="121"/>
-      <c r="P87" s="121"/>
-      <c r="Q87" s="121"/>
-      <c r="R87" s="121"/>
-      <c r="S87" s="121"/>
-      <c r="T87" s="121"/>
+      <c r="B87" s="119"/>
+      <c r="C87" s="119"/>
+      <c r="D87" s="119"/>
+      <c r="E87" s="119"/>
+      <c r="F87" s="119"/>
+      <c r="G87" s="119"/>
+      <c r="H87" s="119"/>
+      <c r="I87" s="119"/>
+      <c r="J87" s="119"/>
+      <c r="K87" s="119"/>
+      <c r="L87" s="119"/>
+      <c r="M87" s="119"/>
+      <c r="N87" s="119"/>
+      <c r="O87" s="119"/>
+      <c r="P87" s="119"/>
+      <c r="Q87" s="119"/>
+      <c r="R87" s="119"/>
+      <c r="S87" s="119"/>
+      <c r="T87" s="119"/>
       <c r="U87" s="10"/>
       <c r="V87" s="10"/>
       <c r="W87" s="10"/>
       <c r="X87" s="10"/>
       <c r="Y87" s="10"/>
       <c r="Z87" s="10"/>
-      <c r="AA87" s="117"/>
-      <c r="AB87" s="118"/>
+      <c r="AA87" s="120"/>
+      <c r="AB87" s="121"/>
       <c r="AC87" s="103"/>
-      <c r="AE87" s="119" t="s">
+      <c r="AE87" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF87" s="120"/>
-      <c r="AG87" s="120"/>
-      <c r="AH87" s="120"/>
-      <c r="AI87" s="120"/>
-      <c r="AJ87" s="120"/>
-      <c r="AK87" s="120"/>
-      <c r="AL87" s="120"/>
-      <c r="AM87" s="120"/>
-      <c r="AN87" s="120"/>
-      <c r="AO87" s="120"/>
-      <c r="AP87" s="120"/>
-      <c r="AQ87" s="120"/>
-      <c r="AR87" s="120"/>
-      <c r="AS87" s="120"/>
+      <c r="AF87" s="118"/>
+      <c r="AG87" s="118"/>
+      <c r="AH87" s="118"/>
+      <c r="AI87" s="118"/>
+      <c r="AJ87" s="118"/>
+      <c r="AK87" s="118"/>
+      <c r="AL87" s="118"/>
+      <c r="AM87" s="118"/>
+      <c r="AN87" s="118"/>
+      <c r="AO87" s="118"/>
+      <c r="AP87" s="118"/>
+      <c r="AQ87" s="118"/>
+      <c r="AR87" s="118"/>
+      <c r="AS87" s="118"/>
     </row>
     <row r="88" spans="1:46" ht="43.8" thickBot="1">
       <c r="A88" s="11" t="s">
@@ -8888,54 +8899,54 @@
       </c>
     </row>
     <row r="103" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A103" s="121" t="s">
+      <c r="A103" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="B103" s="121"/>
-      <c r="C103" s="121"/>
-      <c r="D103" s="121"/>
-      <c r="E103" s="121"/>
-      <c r="F103" s="121"/>
-      <c r="G103" s="121"/>
-      <c r="H103" s="121"/>
-      <c r="I103" s="121"/>
-      <c r="J103" s="121"/>
-      <c r="K103" s="121"/>
-      <c r="L103" s="121"/>
-      <c r="M103" s="121"/>
-      <c r="N103" s="121"/>
-      <c r="O103" s="121"/>
-      <c r="P103" s="121"/>
-      <c r="Q103" s="121"/>
-      <c r="R103" s="121"/>
-      <c r="S103" s="121"/>
-      <c r="T103" s="121"/>
+      <c r="B103" s="119"/>
+      <c r="C103" s="119"/>
+      <c r="D103" s="119"/>
+      <c r="E103" s="119"/>
+      <c r="F103" s="119"/>
+      <c r="G103" s="119"/>
+      <c r="H103" s="119"/>
+      <c r="I103" s="119"/>
+      <c r="J103" s="119"/>
+      <c r="K103" s="119"/>
+      <c r="L103" s="119"/>
+      <c r="M103" s="119"/>
+      <c r="N103" s="119"/>
+      <c r="O103" s="119"/>
+      <c r="P103" s="119"/>
+      <c r="Q103" s="119"/>
+      <c r="R103" s="119"/>
+      <c r="S103" s="119"/>
+      <c r="T103" s="119"/>
       <c r="U103" s="10"/>
       <c r="V103" s="10"/>
       <c r="W103" s="10"/>
       <c r="X103" s="10"/>
       <c r="Y103" s="10"/>
       <c r="Z103" s="10"/>
-      <c r="AA103" s="117"/>
-      <c r="AB103" s="118"/>
+      <c r="AA103" s="120"/>
+      <c r="AB103" s="121"/>
       <c r="AC103" s="103"/>
-      <c r="AE103" s="119" t="s">
+      <c r="AE103" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF103" s="120"/>
-      <c r="AG103" s="120"/>
-      <c r="AH103" s="120"/>
-      <c r="AI103" s="120"/>
-      <c r="AJ103" s="120"/>
-      <c r="AK103" s="120"/>
-      <c r="AL103" s="120"/>
-      <c r="AM103" s="120"/>
-      <c r="AN103" s="120"/>
-      <c r="AO103" s="120"/>
-      <c r="AP103" s="120"/>
-      <c r="AQ103" s="120"/>
-      <c r="AR103" s="120"/>
-      <c r="AS103" s="120"/>
+      <c r="AF103" s="118"/>
+      <c r="AG103" s="118"/>
+      <c r="AH103" s="118"/>
+      <c r="AI103" s="118"/>
+      <c r="AJ103" s="118"/>
+      <c r="AK103" s="118"/>
+      <c r="AL103" s="118"/>
+      <c r="AM103" s="118"/>
+      <c r="AN103" s="118"/>
+      <c r="AO103" s="118"/>
+      <c r="AP103" s="118"/>
+      <c r="AQ103" s="118"/>
+      <c r="AR103" s="118"/>
+      <c r="AS103" s="118"/>
     </row>
     <row r="104" spans="1:45" ht="43.8" thickBot="1">
       <c r="A104" s="11" t="s">
@@ -10082,54 +10093,54 @@
       </c>
     </row>
     <row r="120" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A120" s="121" t="s">
+      <c r="A120" s="119" t="s">
         <v>123</v>
       </c>
-      <c r="B120" s="121"/>
-      <c r="C120" s="121"/>
-      <c r="D120" s="121"/>
-      <c r="E120" s="121"/>
-      <c r="F120" s="121"/>
-      <c r="G120" s="121"/>
-      <c r="H120" s="121"/>
-      <c r="I120" s="121"/>
-      <c r="J120" s="121"/>
-      <c r="K120" s="121"/>
-      <c r="L120" s="121"/>
-      <c r="M120" s="121"/>
-      <c r="N120" s="121"/>
-      <c r="O120" s="121"/>
-      <c r="P120" s="121"/>
-      <c r="Q120" s="121"/>
-      <c r="R120" s="121"/>
-      <c r="S120" s="121"/>
-      <c r="T120" s="121"/>
+      <c r="B120" s="119"/>
+      <c r="C120" s="119"/>
+      <c r="D120" s="119"/>
+      <c r="E120" s="119"/>
+      <c r="F120" s="119"/>
+      <c r="G120" s="119"/>
+      <c r="H120" s="119"/>
+      <c r="I120" s="119"/>
+      <c r="J120" s="119"/>
+      <c r="K120" s="119"/>
+      <c r="L120" s="119"/>
+      <c r="M120" s="119"/>
+      <c r="N120" s="119"/>
+      <c r="O120" s="119"/>
+      <c r="P120" s="119"/>
+      <c r="Q120" s="119"/>
+      <c r="R120" s="119"/>
+      <c r="S120" s="119"/>
+      <c r="T120" s="119"/>
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
       <c r="W120" s="10"/>
       <c r="X120" s="10"/>
       <c r="Y120" s="10"/>
       <c r="Z120" s="10"/>
-      <c r="AA120" s="117"/>
-      <c r="AB120" s="118"/>
+      <c r="AA120" s="120"/>
+      <c r="AB120" s="121"/>
       <c r="AC120" s="103"/>
-      <c r="AE120" s="119" t="s">
+      <c r="AE120" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF120" s="120"/>
-      <c r="AG120" s="120"/>
-      <c r="AH120" s="120"/>
-      <c r="AI120" s="120"/>
-      <c r="AJ120" s="120"/>
-      <c r="AK120" s="120"/>
-      <c r="AL120" s="120"/>
-      <c r="AM120" s="120"/>
-      <c r="AN120" s="120"/>
-      <c r="AO120" s="120"/>
-      <c r="AP120" s="120"/>
-      <c r="AQ120" s="120"/>
-      <c r="AR120" s="120"/>
-      <c r="AS120" s="120"/>
+      <c r="AF120" s="118"/>
+      <c r="AG120" s="118"/>
+      <c r="AH120" s="118"/>
+      <c r="AI120" s="118"/>
+      <c r="AJ120" s="118"/>
+      <c r="AK120" s="118"/>
+      <c r="AL120" s="118"/>
+      <c r="AM120" s="118"/>
+      <c r="AN120" s="118"/>
+      <c r="AO120" s="118"/>
+      <c r="AP120" s="118"/>
+      <c r="AQ120" s="118"/>
+      <c r="AR120" s="118"/>
+      <c r="AS120" s="118"/>
     </row>
     <row r="121" spans="1:45" ht="43.8" thickBot="1">
       <c r="A121" s="11" t="s">
@@ -11051,7 +11062,7 @@
         <v>134</v>
       </c>
       <c r="X131" s="113" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y131" s="33"/>
       <c r="Z131" s="33"/>
@@ -11321,54 +11332,54 @@
       <c r="E138" s="110"/>
     </row>
     <row r="139" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A139" s="121" t="s">
+      <c r="A139" s="119" t="s">
         <v>140</v>
       </c>
-      <c r="B139" s="121"/>
-      <c r="C139" s="121"/>
-      <c r="D139" s="121"/>
-      <c r="E139" s="121"/>
-      <c r="F139" s="121"/>
-      <c r="G139" s="121"/>
-      <c r="H139" s="121"/>
-      <c r="I139" s="121"/>
-      <c r="J139" s="121"/>
-      <c r="K139" s="121"/>
-      <c r="L139" s="121"/>
-      <c r="M139" s="121"/>
-      <c r="N139" s="121"/>
-      <c r="O139" s="121"/>
-      <c r="P139" s="121"/>
-      <c r="Q139" s="121"/>
-      <c r="R139" s="121"/>
-      <c r="S139" s="121"/>
-      <c r="T139" s="121"/>
+      <c r="B139" s="119"/>
+      <c r="C139" s="119"/>
+      <c r="D139" s="119"/>
+      <c r="E139" s="119"/>
+      <c r="F139" s="119"/>
+      <c r="G139" s="119"/>
+      <c r="H139" s="119"/>
+      <c r="I139" s="119"/>
+      <c r="J139" s="119"/>
+      <c r="K139" s="119"/>
+      <c r="L139" s="119"/>
+      <c r="M139" s="119"/>
+      <c r="N139" s="119"/>
+      <c r="O139" s="119"/>
+      <c r="P139" s="119"/>
+      <c r="Q139" s="119"/>
+      <c r="R139" s="119"/>
+      <c r="S139" s="119"/>
+      <c r="T139" s="119"/>
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
       <c r="W139" s="10"/>
       <c r="X139" s="10"/>
       <c r="Y139" s="10"/>
       <c r="Z139" s="10"/>
-      <c r="AA139" s="117"/>
-      <c r="AB139" s="118"/>
+      <c r="AA139" s="120"/>
+      <c r="AB139" s="121"/>
       <c r="AC139" s="103"/>
-      <c r="AE139" s="119" t="s">
+      <c r="AE139" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF139" s="120"/>
-      <c r="AG139" s="120"/>
-      <c r="AH139" s="120"/>
-      <c r="AI139" s="120"/>
-      <c r="AJ139" s="120"/>
-      <c r="AK139" s="120"/>
-      <c r="AL139" s="120"/>
-      <c r="AM139" s="120"/>
-      <c r="AN139" s="120"/>
-      <c r="AO139" s="120"/>
-      <c r="AP139" s="120"/>
-      <c r="AQ139" s="120"/>
-      <c r="AR139" s="120"/>
-      <c r="AS139" s="120"/>
+      <c r="AF139" s="118"/>
+      <c r="AG139" s="118"/>
+      <c r="AH139" s="118"/>
+      <c r="AI139" s="118"/>
+      <c r="AJ139" s="118"/>
+      <c r="AK139" s="118"/>
+      <c r="AL139" s="118"/>
+      <c r="AM139" s="118"/>
+      <c r="AN139" s="118"/>
+      <c r="AO139" s="118"/>
+      <c r="AP139" s="118"/>
+      <c r="AQ139" s="118"/>
+      <c r="AR139" s="118"/>
+      <c r="AS139" s="118"/>
     </row>
     <row r="140" spans="1:45" ht="43.8" thickBot="1">
       <c r="A140" s="11" t="s">
@@ -12556,54 +12567,54 @@
       </c>
     </row>
     <row r="158" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A158" s="121" t="s">
+      <c r="A158" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="B158" s="121"/>
-      <c r="C158" s="121"/>
-      <c r="D158" s="121"/>
-      <c r="E158" s="121"/>
-      <c r="F158" s="121"/>
-      <c r="G158" s="121"/>
-      <c r="H158" s="121"/>
-      <c r="I158" s="121"/>
-      <c r="J158" s="121"/>
-      <c r="K158" s="121"/>
-      <c r="L158" s="121"/>
-      <c r="M158" s="121"/>
-      <c r="N158" s="121"/>
-      <c r="O158" s="121"/>
-      <c r="P158" s="121"/>
-      <c r="Q158" s="121"/>
-      <c r="R158" s="121"/>
-      <c r="S158" s="121"/>
-      <c r="T158" s="121"/>
+      <c r="B158" s="119"/>
+      <c r="C158" s="119"/>
+      <c r="D158" s="119"/>
+      <c r="E158" s="119"/>
+      <c r="F158" s="119"/>
+      <c r="G158" s="119"/>
+      <c r="H158" s="119"/>
+      <c r="I158" s="119"/>
+      <c r="J158" s="119"/>
+      <c r="K158" s="119"/>
+      <c r="L158" s="119"/>
+      <c r="M158" s="119"/>
+      <c r="N158" s="119"/>
+      <c r="O158" s="119"/>
+      <c r="P158" s="119"/>
+      <c r="Q158" s="119"/>
+      <c r="R158" s="119"/>
+      <c r="S158" s="119"/>
+      <c r="T158" s="119"/>
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
       <c r="W158" s="10"/>
       <c r="X158" s="10"/>
       <c r="Y158" s="10"/>
       <c r="Z158" s="10"/>
-      <c r="AA158" s="117"/>
-      <c r="AB158" s="118"/>
+      <c r="AA158" s="120"/>
+      <c r="AB158" s="121"/>
       <c r="AC158" s="103"/>
-      <c r="AE158" s="119" t="s">
+      <c r="AE158" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF158" s="120"/>
-      <c r="AG158" s="120"/>
-      <c r="AH158" s="120"/>
-      <c r="AI158" s="120"/>
-      <c r="AJ158" s="120"/>
-      <c r="AK158" s="120"/>
-      <c r="AL158" s="120"/>
-      <c r="AM158" s="120"/>
-      <c r="AN158" s="120"/>
-      <c r="AO158" s="120"/>
-      <c r="AP158" s="120"/>
-      <c r="AQ158" s="120"/>
-      <c r="AR158" s="120"/>
-      <c r="AS158" s="120"/>
+      <c r="AF158" s="118"/>
+      <c r="AG158" s="118"/>
+      <c r="AH158" s="118"/>
+      <c r="AI158" s="118"/>
+      <c r="AJ158" s="118"/>
+      <c r="AK158" s="118"/>
+      <c r="AL158" s="118"/>
+      <c r="AM158" s="118"/>
+      <c r="AN158" s="118"/>
+      <c r="AO158" s="118"/>
+      <c r="AP158" s="118"/>
+      <c r="AQ158" s="118"/>
+      <c r="AR158" s="118"/>
+      <c r="AS158" s="118"/>
     </row>
     <row r="159" spans="1:45" ht="43.8" thickBot="1">
       <c r="A159" s="11" t="s">
@@ -13516,10 +13527,10 @@
         <v>170</v>
       </c>
       <c r="W169" s="113" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X169" s="113" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y169" s="113" t="s">
         <v>166</v>
@@ -13752,54 +13763,54 @@
       </c>
     </row>
     <row r="174" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A174" s="121" t="s">
+      <c r="A174" s="119" t="s">
         <v>161</v>
       </c>
-      <c r="B174" s="121"/>
-      <c r="C174" s="121"/>
-      <c r="D174" s="121"/>
-      <c r="E174" s="121"/>
-      <c r="F174" s="121"/>
-      <c r="G174" s="121"/>
-      <c r="H174" s="121"/>
-      <c r="I174" s="121"/>
-      <c r="J174" s="121"/>
-      <c r="K174" s="121"/>
-      <c r="L174" s="121"/>
-      <c r="M174" s="121"/>
-      <c r="N174" s="121"/>
-      <c r="O174" s="121"/>
-      <c r="P174" s="121"/>
-      <c r="Q174" s="121"/>
-      <c r="R174" s="121"/>
-      <c r="S174" s="121"/>
-      <c r="T174" s="121"/>
+      <c r="B174" s="119"/>
+      <c r="C174" s="119"/>
+      <c r="D174" s="119"/>
+      <c r="E174" s="119"/>
+      <c r="F174" s="119"/>
+      <c r="G174" s="119"/>
+      <c r="H174" s="119"/>
+      <c r="I174" s="119"/>
+      <c r="J174" s="119"/>
+      <c r="K174" s="119"/>
+      <c r="L174" s="119"/>
+      <c r="M174" s="119"/>
+      <c r="N174" s="119"/>
+      <c r="O174" s="119"/>
+      <c r="P174" s="119"/>
+      <c r="Q174" s="119"/>
+      <c r="R174" s="119"/>
+      <c r="S174" s="119"/>
+      <c r="T174" s="119"/>
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
       <c r="W174" s="10"/>
       <c r="X174" s="10"/>
       <c r="Y174" s="10"/>
       <c r="Z174" s="10"/>
-      <c r="AA174" s="117"/>
-      <c r="AB174" s="118"/>
+      <c r="AA174" s="120"/>
+      <c r="AB174" s="121"/>
       <c r="AC174" s="103"/>
-      <c r="AE174" s="119" t="s">
+      <c r="AE174" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF174" s="120"/>
-      <c r="AG174" s="120"/>
-      <c r="AH174" s="120"/>
-      <c r="AI174" s="120"/>
-      <c r="AJ174" s="120"/>
-      <c r="AK174" s="120"/>
-      <c r="AL174" s="120"/>
-      <c r="AM174" s="120"/>
-      <c r="AN174" s="120"/>
-      <c r="AO174" s="120"/>
-      <c r="AP174" s="120"/>
-      <c r="AQ174" s="120"/>
-      <c r="AR174" s="120"/>
-      <c r="AS174" s="120"/>
+      <c r="AF174" s="118"/>
+      <c r="AG174" s="118"/>
+      <c r="AH174" s="118"/>
+      <c r="AI174" s="118"/>
+      <c r="AJ174" s="118"/>
+      <c r="AK174" s="118"/>
+      <c r="AL174" s="118"/>
+      <c r="AM174" s="118"/>
+      <c r="AN174" s="118"/>
+      <c r="AO174" s="118"/>
+      <c r="AP174" s="118"/>
+      <c r="AQ174" s="118"/>
+      <c r="AR174" s="118"/>
+      <c r="AS174" s="118"/>
     </row>
     <row r="175" spans="1:45" ht="43.8" thickBot="1">
       <c r="A175" s="11" t="s">
@@ -14696,7 +14707,7 @@
         <v>182</v>
       </c>
       <c r="Y185" s="113" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z185" s="33"/>
       <c r="AA185" s="33"/>
@@ -14952,54 +14963,54 @@
       </c>
     </row>
     <row r="192" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A192" s="121" t="s">
+      <c r="A192" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="B192" s="121"/>
-      <c r="C192" s="121"/>
-      <c r="D192" s="121"/>
-      <c r="E192" s="121"/>
-      <c r="F192" s="121"/>
-      <c r="G192" s="121"/>
-      <c r="H192" s="121"/>
-      <c r="I192" s="121"/>
-      <c r="J192" s="121"/>
-      <c r="K192" s="121"/>
-      <c r="L192" s="121"/>
-      <c r="M192" s="121"/>
-      <c r="N192" s="121"/>
-      <c r="O192" s="121"/>
-      <c r="P192" s="121"/>
-      <c r="Q192" s="121"/>
-      <c r="R192" s="121"/>
-      <c r="S192" s="121"/>
-      <c r="T192" s="121"/>
+      <c r="B192" s="119"/>
+      <c r="C192" s="119"/>
+      <c r="D192" s="119"/>
+      <c r="E192" s="119"/>
+      <c r="F192" s="119"/>
+      <c r="G192" s="119"/>
+      <c r="H192" s="119"/>
+      <c r="I192" s="119"/>
+      <c r="J192" s="119"/>
+      <c r="K192" s="119"/>
+      <c r="L192" s="119"/>
+      <c r="M192" s="119"/>
+      <c r="N192" s="119"/>
+      <c r="O192" s="119"/>
+      <c r="P192" s="119"/>
+      <c r="Q192" s="119"/>
+      <c r="R192" s="119"/>
+      <c r="S192" s="119"/>
+      <c r="T192" s="119"/>
       <c r="U192" s="10"/>
       <c r="V192" s="10"/>
       <c r="W192" s="10"/>
       <c r="X192" s="10"/>
       <c r="Y192" s="10"/>
       <c r="Z192" s="10"/>
-      <c r="AA192" s="117"/>
-      <c r="AB192" s="118"/>
+      <c r="AA192" s="120"/>
+      <c r="AB192" s="121"/>
       <c r="AC192" s="103"/>
-      <c r="AE192" s="119" t="s">
+      <c r="AE192" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AF192" s="120"/>
-      <c r="AG192" s="120"/>
-      <c r="AH192" s="120"/>
-      <c r="AI192" s="120"/>
-      <c r="AJ192" s="120"/>
-      <c r="AK192" s="120"/>
-      <c r="AL192" s="120"/>
-      <c r="AM192" s="120"/>
-      <c r="AN192" s="120"/>
-      <c r="AO192" s="120"/>
-      <c r="AP192" s="120"/>
-      <c r="AQ192" s="120"/>
-      <c r="AR192" s="120"/>
-      <c r="AS192" s="120"/>
+      <c r="AF192" s="118"/>
+      <c r="AG192" s="118"/>
+      <c r="AH192" s="118"/>
+      <c r="AI192" s="118"/>
+      <c r="AJ192" s="118"/>
+      <c r="AK192" s="118"/>
+      <c r="AL192" s="118"/>
+      <c r="AM192" s="118"/>
+      <c r="AN192" s="118"/>
+      <c r="AO192" s="118"/>
+      <c r="AP192" s="118"/>
+      <c r="AQ192" s="118"/>
+      <c r="AR192" s="118"/>
+      <c r="AS192" s="118"/>
     </row>
     <row r="193" spans="1:45" ht="43.8" thickBot="1">
       <c r="A193" s="11" t="s">
@@ -15185,7 +15196,9 @@
       <c r="R194" s="14">
         <v>21852.5</v>
       </c>
-      <c r="S194" s="14"/>
+      <c r="S194" s="14">
+        <v>212179</v>
+      </c>
       <c r="T194" s="14">
         <v>214017.13</v>
       </c>
@@ -15620,7 +15633,7 @@
       </c>
       <c r="S200" s="6">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>212179</v>
       </c>
       <c r="T200" s="6">
         <f t="shared" si="102"/>
@@ -15791,7 +15804,7 @@
       </c>
       <c r="S202" s="54">
         <f>(S201-S200)</f>
-        <v>212179.1</v>
+        <v>0.10000000000582077</v>
       </c>
       <c r="T202" s="54">
         <f t="shared" ref="T202:U202" si="107">(T201-T200)</f>
@@ -15881,28 +15894,28 @@
         <v>185</v>
       </c>
       <c r="X203" s="113" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y203" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="Y203" s="113" t="s">
+      <c r="Z203" s="113" t="s">
         <v>194</v>
       </c>
-      <c r="Z203" s="113" t="s">
+      <c r="AA203" s="113" t="s">
         <v>195</v>
       </c>
-      <c r="AA203" s="113" t="s">
+      <c r="AB203" s="113" t="s">
         <v>196</v>
       </c>
-      <c r="AB203" s="113" t="s">
+      <c r="AC203" s="113" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD203" s="113" t="s">
         <v>197</v>
       </c>
-      <c r="AC203" s="113" t="s">
-        <v>200</v>
-      </c>
-      <c r="AD203" s="113" t="s">
+      <c r="AE203" s="113" t="s">
         <v>198</v>
-      </c>
-      <c r="AE203" s="113" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="204" spans="1:45">
@@ -16114,14 +16127,14 @@
       </c>
       <c r="J206" s="60">
         <f>SUM(G200:V200)-AD204</f>
-        <v>1680617.6999999997</v>
+        <v>1892796.6999999997</v>
       </c>
       <c r="L206" s="67" t="s">
         <v>77</v>
       </c>
       <c r="M206" s="68">
         <f>(G206-J206)</f>
-        <v>258459.16000000061</v>
+        <v>46280.160000000615</v>
       </c>
       <c r="O206" s="61" t="s">
         <v>95</v>
@@ -16179,42 +16192,34 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="AE103:AS103"/>
-    <mergeCell ref="AE120:AS120"/>
-    <mergeCell ref="AE37:AS37"/>
-    <mergeCell ref="AE54:AS54"/>
-    <mergeCell ref="AE69:AS69"/>
-    <mergeCell ref="AE87:AS87"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="M103:P103"/>
-    <mergeCell ref="Q103:T103"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q54:T54"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="M87:P87"/>
-    <mergeCell ref="Q87:T87"/>
+    <mergeCell ref="AA192:AB192"/>
+    <mergeCell ref="AE192:AS192"/>
+    <mergeCell ref="A192:D192"/>
+    <mergeCell ref="E192:H192"/>
+    <mergeCell ref="I192:L192"/>
+    <mergeCell ref="M192:P192"/>
+    <mergeCell ref="Q192:T192"/>
+    <mergeCell ref="AA174:AB174"/>
+    <mergeCell ref="AE174:AS174"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="E174:H174"/>
+    <mergeCell ref="I174:L174"/>
+    <mergeCell ref="M174:P174"/>
+    <mergeCell ref="Q174:T174"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="AE158:AS158"/>
+    <mergeCell ref="AA158:AB158"/>
+    <mergeCell ref="Q158:T158"/>
+    <mergeCell ref="M158:P158"/>
+    <mergeCell ref="I158:L158"/>
+    <mergeCell ref="AA139:AB139"/>
+    <mergeCell ref="AE139:AS139"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="M139:P139"/>
+    <mergeCell ref="Q139:T139"/>
     <mergeCell ref="AA120:AB120"/>
     <mergeCell ref="AE2:AS2"/>
     <mergeCell ref="AE21:AS21"/>
@@ -16231,34 +16236,42 @@
     <mergeCell ref="I69:L69"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="AA139:AB139"/>
-    <mergeCell ref="AE139:AS139"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="M139:P139"/>
-    <mergeCell ref="Q139:T139"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="A158:D158"/>
-    <mergeCell ref="AE158:AS158"/>
-    <mergeCell ref="AA158:AB158"/>
-    <mergeCell ref="Q158:T158"/>
-    <mergeCell ref="M158:P158"/>
-    <mergeCell ref="I158:L158"/>
-    <mergeCell ref="AA174:AB174"/>
-    <mergeCell ref="AE174:AS174"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="E174:H174"/>
-    <mergeCell ref="I174:L174"/>
-    <mergeCell ref="M174:P174"/>
-    <mergeCell ref="Q174:T174"/>
-    <mergeCell ref="AA192:AB192"/>
-    <mergeCell ref="AE192:AS192"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="E192:H192"/>
-    <mergeCell ref="I192:L192"/>
-    <mergeCell ref="M192:P192"/>
-    <mergeCell ref="Q192:T192"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="M87:P87"/>
+    <mergeCell ref="Q87:T87"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q54:T54"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="M103:P103"/>
+    <mergeCell ref="Q103:T103"/>
+    <mergeCell ref="AE103:AS103"/>
+    <mergeCell ref="AE120:AS120"/>
+    <mergeCell ref="AE37:AS37"/>
+    <mergeCell ref="AE54:AS54"/>
+    <mergeCell ref="AE69:AS69"/>
+    <mergeCell ref="AE87:AS87"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16740,7 +16753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F2BD5F-5FC8-4604-BC5A-7F98636B3F60}">
-  <dimension ref="C2:D32"/>
+  <dimension ref="C2:D36"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.5546875" customWidth="1"/>
@@ -16748,91 +16761,91 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:4">
-      <c r="C2" t="s">
-        <v>186</v>
+      <c r="C2" s="116" t="s">
+        <v>155</v>
       </c>
       <c r="D2">
-        <v>1377415</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="3" spans="3:4">
       <c r="C3" s="116" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D3">
-        <v>45000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="4" spans="3:4">
       <c r="C4" s="116" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="D4">
-        <v>10800</v>
+        <v>12555</v>
       </c>
     </row>
     <row r="5" spans="3:4">
       <c r="C5" s="116" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D5">
-        <v>12555</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="6" spans="3:4">
       <c r="C6" s="116" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D6">
-        <v>13500</v>
+        <v>48500</v>
       </c>
     </row>
     <row r="7" spans="3:4">
       <c r="C7" s="116" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D7">
-        <v>48500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="8" spans="3:4">
       <c r="C8" s="116" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="D8">
-        <v>18000</v>
+        <v>23163</v>
       </c>
     </row>
     <row r="9" spans="3:4">
       <c r="C9" s="116" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="D9">
-        <v>23163</v>
+        <v>50976</v>
       </c>
     </row>
     <row r="10" spans="3:4">
       <c r="C10" s="116" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D10">
-        <v>50976</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4">
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" ht="18" customHeight="1">
       <c r="C11" s="116" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D11">
-        <v>18880</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" ht="18" customHeight="1">
+        <v>219000</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4">
       <c r="C12" s="116" t="s">
         <v>188</v>
       </c>
       <c r="D12">
-        <v>219000</v>
+        <v>169250</v>
       </c>
     </row>
     <row r="13" spans="3:4">
@@ -16840,95 +16853,95 @@
         <v>189</v>
       </c>
       <c r="D13">
-        <v>169250</v>
+        <v>87108</v>
       </c>
     </row>
     <row r="14" spans="3:4">
       <c r="C14" s="116" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D14">
-        <v>87108</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="15" spans="3:4">
       <c r="C15" s="116" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D15">
-        <v>70800</v>
+        <v>107500</v>
       </c>
     </row>
     <row r="16" spans="3:4">
       <c r="C16" s="116" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D16">
-        <v>107500</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="17" spans="3:4">
       <c r="C17" s="116" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D17">
-        <v>5900</v>
+        <v>193000</v>
       </c>
     </row>
     <row r="18" spans="3:4">
       <c r="C18" s="116" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D18">
-        <v>193000</v>
+        <v>29880</v>
       </c>
     </row>
     <row r="19" spans="3:4">
       <c r="C19" s="116" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D19">
-        <v>29880</v>
+        <v>9190</v>
       </c>
     </row>
     <row r="20" spans="3:4">
       <c r="C20" s="116" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D20">
-        <v>9190</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4">
+        <v>15540</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" ht="28.8">
       <c r="C21" s="116" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D21">
-        <v>15540</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" ht="28.8">
+        <v>11965</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4">
       <c r="C22" s="116" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D22">
-        <v>11965</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" ht="28.8">
       <c r="C23" s="116" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D23">
-        <v>5900</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" ht="28.8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4">
       <c r="C24" s="116" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>28260</v>
       </c>
     </row>
     <row r="25" spans="3:4">
@@ -16936,7 +16949,7 @@
         <v>193</v>
       </c>
       <c r="D25">
-        <v>28260</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="26" spans="3:4">
@@ -16944,7 +16957,7 @@
         <v>194</v>
       </c>
       <c r="D26">
-        <v>45000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="27" spans="3:4">
@@ -16952,47 +16965,79 @@
         <v>195</v>
       </c>
       <c r="D27">
-        <v>6000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="116" t="s">
+      <c r="C28" t="s">
         <v>196</v>
       </c>
       <c r="D28">
-        <v>43000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29" spans="3:4">
       <c r="C29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29">
+        <v>12914</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="116" t="s">
         <v>197</v>
       </c>
-      <c r="D29">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4">
-      <c r="C30" t="s">
-        <v>200</v>
-      </c>
       <c r="D30">
-        <v>12914</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="116" t="s">
+      <c r="C31" t="s">
         <v>198</v>
       </c>
       <c r="D31">
-        <v>1200</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="32" spans="3:4">
       <c r="C32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D32">
-        <v>3190</v>
+        <v>23302</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" s="116" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34">
+        <v>27685</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35">
+        <v>174800</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36">
+        <v>183250</v>
       </c>
     </row>
   </sheetData>

--- a/Zen_Estate_Combined_Expenses_Q1.xlsx
+++ b/Zen_Estate_Combined_Expenses_Q1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1065D89E-D6D8-4C79-A1E8-A2DEE0AABE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153A5FDE-60B4-46BC-878E-F0E0C72C4823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1574,6 +1574,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1581,12 +1587,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1955,28 +1955,28 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
@@ -3127,28 +3127,28 @@
       </c>
     </row>
     <row r="21" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="119"/>
-      <c r="S21" s="119"/>
-      <c r="T21" s="119"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="121"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -4250,28 +4250,28 @@
       </c>
     </row>
     <row r="37" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A37" s="119" t="s">
+      <c r="A37" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="119"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="119"/>
-      <c r="L37" s="119"/>
-      <c r="M37" s="119"/>
-      <c r="N37" s="119"/>
-      <c r="O37" s="119"/>
-      <c r="P37" s="119"/>
-      <c r="Q37" s="119"/>
-      <c r="R37" s="119"/>
-      <c r="S37" s="119"/>
-      <c r="T37" s="119"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="121"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
@@ -4281,23 +4281,23 @@
       <c r="AA37" s="34"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="34"/>
-      <c r="AE37" s="117" t="s">
+      <c r="AE37" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF37" s="118"/>
-      <c r="AG37" s="118"/>
-      <c r="AH37" s="118"/>
-      <c r="AI37" s="118"/>
-      <c r="AJ37" s="118"/>
-      <c r="AK37" s="118"/>
-      <c r="AL37" s="118"/>
-      <c r="AM37" s="118"/>
-      <c r="AN37" s="118"/>
-      <c r="AO37" s="118"/>
-      <c r="AP37" s="118"/>
-      <c r="AQ37" s="118"/>
-      <c r="AR37" s="118"/>
-      <c r="AS37" s="118"/>
+      <c r="AF37" s="120"/>
+      <c r="AG37" s="120"/>
+      <c r="AH37" s="120"/>
+      <c r="AI37" s="120"/>
+      <c r="AJ37" s="120"/>
+      <c r="AK37" s="120"/>
+      <c r="AL37" s="120"/>
+      <c r="AM37" s="120"/>
+      <c r="AN37" s="120"/>
+      <c r="AO37" s="120"/>
+      <c r="AP37" s="120"/>
+      <c r="AQ37" s="120"/>
+      <c r="AR37" s="120"/>
+      <c r="AS37" s="120"/>
     </row>
     <row r="38" spans="1:46" ht="15" thickBot="1">
       <c r="A38" s="11" t="s">
@@ -5418,51 +5418,51 @@
       </c>
     </row>
     <row r="54" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A54" s="119" t="s">
+      <c r="A54" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="119"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="119"/>
-      <c r="K54" s="119"/>
-      <c r="L54" s="119"/>
-      <c r="M54" s="119"/>
-      <c r="N54" s="119"/>
-      <c r="O54" s="119"/>
-      <c r="P54" s="119"/>
-      <c r="Q54" s="119"/>
-      <c r="R54" s="119"/>
-      <c r="S54" s="119"/>
-      <c r="T54" s="119"/>
+      <c r="B54" s="121"/>
+      <c r="C54" s="121"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="121"/>
+      <c r="I54" s="121"/>
+      <c r="J54" s="121"/>
+      <c r="K54" s="121"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="121"/>
+      <c r="R54" s="121"/>
+      <c r="S54" s="121"/>
+      <c r="T54" s="121"/>
       <c r="U54" s="10"/>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
       <c r="X54" s="82"/>
       <c r="Y54" s="82"/>
       <c r="Z54" s="83"/>
-      <c r="AE54" s="117" t="s">
+      <c r="AE54" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF54" s="118"/>
-      <c r="AG54" s="118"/>
-      <c r="AH54" s="118"/>
-      <c r="AI54" s="118"/>
-      <c r="AJ54" s="118"/>
-      <c r="AK54" s="118"/>
-      <c r="AL54" s="118"/>
-      <c r="AM54" s="118"/>
-      <c r="AN54" s="118"/>
-      <c r="AO54" s="118"/>
-      <c r="AP54" s="118"/>
-      <c r="AQ54" s="118"/>
-      <c r="AR54" s="118"/>
-      <c r="AS54" s="118"/>
+      <c r="AF54" s="120"/>
+      <c r="AG54" s="120"/>
+      <c r="AH54" s="120"/>
+      <c r="AI54" s="120"/>
+      <c r="AJ54" s="120"/>
+      <c r="AK54" s="120"/>
+      <c r="AL54" s="120"/>
+      <c r="AM54" s="120"/>
+      <c r="AN54" s="120"/>
+      <c r="AO54" s="120"/>
+      <c r="AP54" s="120"/>
+      <c r="AQ54" s="120"/>
+      <c r="AR54" s="120"/>
+      <c r="AS54" s="120"/>
     </row>
     <row r="55" spans="1:46" ht="15" thickBot="1">
       <c r="A55" s="11" t="s">
@@ -6538,54 +6538,54 @@
       <c r="V68" s="20"/>
     </row>
     <row r="69" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A69" s="119" t="s">
+      <c r="A69" s="121" t="s">
         <v>104</v>
       </c>
-      <c r="B69" s="119"/>
-      <c r="C69" s="119"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="119"/>
-      <c r="H69" s="119"/>
-      <c r="I69" s="119"/>
-      <c r="J69" s="119"/>
-      <c r="K69" s="119"/>
-      <c r="L69" s="119"/>
-      <c r="M69" s="119"/>
-      <c r="N69" s="119"/>
-      <c r="O69" s="119"/>
-      <c r="P69" s="119"/>
-      <c r="Q69" s="119"/>
-      <c r="R69" s="119"/>
-      <c r="S69" s="119"/>
-      <c r="T69" s="119"/>
+      <c r="B69" s="121"/>
+      <c r="C69" s="121"/>
+      <c r="D69" s="121"/>
+      <c r="E69" s="121"/>
+      <c r="F69" s="121"/>
+      <c r="G69" s="121"/>
+      <c r="H69" s="121"/>
+      <c r="I69" s="121"/>
+      <c r="J69" s="121"/>
+      <c r="K69" s="121"/>
+      <c r="L69" s="121"/>
+      <c r="M69" s="121"/>
+      <c r="N69" s="121"/>
+      <c r="O69" s="121"/>
+      <c r="P69" s="121"/>
+      <c r="Q69" s="121"/>
+      <c r="R69" s="121"/>
+      <c r="S69" s="121"/>
+      <c r="T69" s="121"/>
       <c r="U69" s="10"/>
       <c r="V69" s="10"/>
       <c r="W69" s="10"/>
       <c r="X69" s="10"/>
       <c r="Y69" s="10"/>
       <c r="Z69" s="10"/>
-      <c r="AA69" s="120"/>
-      <c r="AB69" s="121"/>
+      <c r="AA69" s="117"/>
+      <c r="AB69" s="118"/>
       <c r="AC69" s="103"/>
-      <c r="AE69" s="117" t="s">
+      <c r="AE69" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF69" s="118"/>
-      <c r="AG69" s="118"/>
-      <c r="AH69" s="118"/>
-      <c r="AI69" s="118"/>
-      <c r="AJ69" s="118"/>
-      <c r="AK69" s="118"/>
-      <c r="AL69" s="118"/>
-      <c r="AM69" s="118"/>
-      <c r="AN69" s="118"/>
-      <c r="AO69" s="118"/>
-      <c r="AP69" s="118"/>
-      <c r="AQ69" s="118"/>
-      <c r="AR69" s="118"/>
-      <c r="AS69" s="118"/>
+      <c r="AF69" s="120"/>
+      <c r="AG69" s="120"/>
+      <c r="AH69" s="120"/>
+      <c r="AI69" s="120"/>
+      <c r="AJ69" s="120"/>
+      <c r="AK69" s="120"/>
+      <c r="AL69" s="120"/>
+      <c r="AM69" s="120"/>
+      <c r="AN69" s="120"/>
+      <c r="AO69" s="120"/>
+      <c r="AP69" s="120"/>
+      <c r="AQ69" s="120"/>
+      <c r="AR69" s="120"/>
+      <c r="AS69" s="120"/>
     </row>
     <row r="70" spans="1:45" ht="43.8" thickBot="1">
       <c r="A70" s="11" t="s">
@@ -7709,54 +7709,54 @@
       </c>
     </row>
     <row r="87" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A87" s="119" t="s">
+      <c r="A87" s="121" t="s">
         <v>109</v>
       </c>
-      <c r="B87" s="119"/>
-      <c r="C87" s="119"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="119"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="119"/>
-      <c r="H87" s="119"/>
-      <c r="I87" s="119"/>
-      <c r="J87" s="119"/>
-      <c r="K87" s="119"/>
-      <c r="L87" s="119"/>
-      <c r="M87" s="119"/>
-      <c r="N87" s="119"/>
-      <c r="O87" s="119"/>
-      <c r="P87" s="119"/>
-      <c r="Q87" s="119"/>
-      <c r="R87" s="119"/>
-      <c r="S87" s="119"/>
-      <c r="T87" s="119"/>
+      <c r="B87" s="121"/>
+      <c r="C87" s="121"/>
+      <c r="D87" s="121"/>
+      <c r="E87" s="121"/>
+      <c r="F87" s="121"/>
+      <c r="G87" s="121"/>
+      <c r="H87" s="121"/>
+      <c r="I87" s="121"/>
+      <c r="J87" s="121"/>
+      <c r="K87" s="121"/>
+      <c r="L87" s="121"/>
+      <c r="M87" s="121"/>
+      <c r="N87" s="121"/>
+      <c r="O87" s="121"/>
+      <c r="P87" s="121"/>
+      <c r="Q87" s="121"/>
+      <c r="R87" s="121"/>
+      <c r="S87" s="121"/>
+      <c r="T87" s="121"/>
       <c r="U87" s="10"/>
       <c r="V87" s="10"/>
       <c r="W87" s="10"/>
       <c r="X87" s="10"/>
       <c r="Y87" s="10"/>
       <c r="Z87" s="10"/>
-      <c r="AA87" s="120"/>
-      <c r="AB87" s="121"/>
+      <c r="AA87" s="117"/>
+      <c r="AB87" s="118"/>
       <c r="AC87" s="103"/>
-      <c r="AE87" s="117" t="s">
+      <c r="AE87" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF87" s="118"/>
-      <c r="AG87" s="118"/>
-      <c r="AH87" s="118"/>
-      <c r="AI87" s="118"/>
-      <c r="AJ87" s="118"/>
-      <c r="AK87" s="118"/>
-      <c r="AL87" s="118"/>
-      <c r="AM87" s="118"/>
-      <c r="AN87" s="118"/>
-      <c r="AO87" s="118"/>
-      <c r="AP87" s="118"/>
-      <c r="AQ87" s="118"/>
-      <c r="AR87" s="118"/>
-      <c r="AS87" s="118"/>
+      <c r="AF87" s="120"/>
+      <c r="AG87" s="120"/>
+      <c r="AH87" s="120"/>
+      <c r="AI87" s="120"/>
+      <c r="AJ87" s="120"/>
+      <c r="AK87" s="120"/>
+      <c r="AL87" s="120"/>
+      <c r="AM87" s="120"/>
+      <c r="AN87" s="120"/>
+      <c r="AO87" s="120"/>
+      <c r="AP87" s="120"/>
+      <c r="AQ87" s="120"/>
+      <c r="AR87" s="120"/>
+      <c r="AS87" s="120"/>
     </row>
     <row r="88" spans="1:46" ht="43.8" thickBot="1">
       <c r="A88" s="11" t="s">
@@ -8899,54 +8899,54 @@
       </c>
     </row>
     <row r="103" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A103" s="119" t="s">
+      <c r="A103" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="B103" s="119"/>
-      <c r="C103" s="119"/>
-      <c r="D103" s="119"/>
-      <c r="E103" s="119"/>
-      <c r="F103" s="119"/>
-      <c r="G103" s="119"/>
-      <c r="H103" s="119"/>
-      <c r="I103" s="119"/>
-      <c r="J103" s="119"/>
-      <c r="K103" s="119"/>
-      <c r="L103" s="119"/>
-      <c r="M103" s="119"/>
-      <c r="N103" s="119"/>
-      <c r="O103" s="119"/>
-      <c r="P103" s="119"/>
-      <c r="Q103" s="119"/>
-      <c r="R103" s="119"/>
-      <c r="S103" s="119"/>
-      <c r="T103" s="119"/>
+      <c r="B103" s="121"/>
+      <c r="C103" s="121"/>
+      <c r="D103" s="121"/>
+      <c r="E103" s="121"/>
+      <c r="F103" s="121"/>
+      <c r="G103" s="121"/>
+      <c r="H103" s="121"/>
+      <c r="I103" s="121"/>
+      <c r="J103" s="121"/>
+      <c r="K103" s="121"/>
+      <c r="L103" s="121"/>
+      <c r="M103" s="121"/>
+      <c r="N103" s="121"/>
+      <c r="O103" s="121"/>
+      <c r="P103" s="121"/>
+      <c r="Q103" s="121"/>
+      <c r="R103" s="121"/>
+      <c r="S103" s="121"/>
+      <c r="T103" s="121"/>
       <c r="U103" s="10"/>
       <c r="V103" s="10"/>
       <c r="W103" s="10"/>
       <c r="X103" s="10"/>
       <c r="Y103" s="10"/>
       <c r="Z103" s="10"/>
-      <c r="AA103" s="120"/>
-      <c r="AB103" s="121"/>
+      <c r="AA103" s="117"/>
+      <c r="AB103" s="118"/>
       <c r="AC103" s="103"/>
-      <c r="AE103" s="117" t="s">
+      <c r="AE103" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF103" s="118"/>
-      <c r="AG103" s="118"/>
-      <c r="AH103" s="118"/>
-      <c r="AI103" s="118"/>
-      <c r="AJ103" s="118"/>
-      <c r="AK103" s="118"/>
-      <c r="AL103" s="118"/>
-      <c r="AM103" s="118"/>
-      <c r="AN103" s="118"/>
-      <c r="AO103" s="118"/>
-      <c r="AP103" s="118"/>
-      <c r="AQ103" s="118"/>
-      <c r="AR103" s="118"/>
-      <c r="AS103" s="118"/>
+      <c r="AF103" s="120"/>
+      <c r="AG103" s="120"/>
+      <c r="AH103" s="120"/>
+      <c r="AI103" s="120"/>
+      <c r="AJ103" s="120"/>
+      <c r="AK103" s="120"/>
+      <c r="AL103" s="120"/>
+      <c r="AM103" s="120"/>
+      <c r="AN103" s="120"/>
+      <c r="AO103" s="120"/>
+      <c r="AP103" s="120"/>
+      <c r="AQ103" s="120"/>
+      <c r="AR103" s="120"/>
+      <c r="AS103" s="120"/>
     </row>
     <row r="104" spans="1:45" ht="43.8" thickBot="1">
       <c r="A104" s="11" t="s">
@@ -10093,54 +10093,54 @@
       </c>
     </row>
     <row r="120" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A120" s="119" t="s">
+      <c r="A120" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="B120" s="119"/>
-      <c r="C120" s="119"/>
-      <c r="D120" s="119"/>
-      <c r="E120" s="119"/>
-      <c r="F120" s="119"/>
-      <c r="G120" s="119"/>
-      <c r="H120" s="119"/>
-      <c r="I120" s="119"/>
-      <c r="J120" s="119"/>
-      <c r="K120" s="119"/>
-      <c r="L120" s="119"/>
-      <c r="M120" s="119"/>
-      <c r="N120" s="119"/>
-      <c r="O120" s="119"/>
-      <c r="P120" s="119"/>
-      <c r="Q120" s="119"/>
-      <c r="R120" s="119"/>
-      <c r="S120" s="119"/>
-      <c r="T120" s="119"/>
+      <c r="B120" s="121"/>
+      <c r="C120" s="121"/>
+      <c r="D120" s="121"/>
+      <c r="E120" s="121"/>
+      <c r="F120" s="121"/>
+      <c r="G120" s="121"/>
+      <c r="H120" s="121"/>
+      <c r="I120" s="121"/>
+      <c r="J120" s="121"/>
+      <c r="K120" s="121"/>
+      <c r="L120" s="121"/>
+      <c r="M120" s="121"/>
+      <c r="N120" s="121"/>
+      <c r="O120" s="121"/>
+      <c r="P120" s="121"/>
+      <c r="Q120" s="121"/>
+      <c r="R120" s="121"/>
+      <c r="S120" s="121"/>
+      <c r="T120" s="121"/>
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
       <c r="W120" s="10"/>
       <c r="X120" s="10"/>
       <c r="Y120" s="10"/>
       <c r="Z120" s="10"/>
-      <c r="AA120" s="120"/>
-      <c r="AB120" s="121"/>
+      <c r="AA120" s="117"/>
+      <c r="AB120" s="118"/>
       <c r="AC120" s="103"/>
-      <c r="AE120" s="117" t="s">
+      <c r="AE120" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF120" s="118"/>
-      <c r="AG120" s="118"/>
-      <c r="AH120" s="118"/>
-      <c r="AI120" s="118"/>
-      <c r="AJ120" s="118"/>
-      <c r="AK120" s="118"/>
-      <c r="AL120" s="118"/>
-      <c r="AM120" s="118"/>
-      <c r="AN120" s="118"/>
-      <c r="AO120" s="118"/>
-      <c r="AP120" s="118"/>
-      <c r="AQ120" s="118"/>
-      <c r="AR120" s="118"/>
-      <c r="AS120" s="118"/>
+      <c r="AF120" s="120"/>
+      <c r="AG120" s="120"/>
+      <c r="AH120" s="120"/>
+      <c r="AI120" s="120"/>
+      <c r="AJ120" s="120"/>
+      <c r="AK120" s="120"/>
+      <c r="AL120" s="120"/>
+      <c r="AM120" s="120"/>
+      <c r="AN120" s="120"/>
+      <c r="AO120" s="120"/>
+      <c r="AP120" s="120"/>
+      <c r="AQ120" s="120"/>
+      <c r="AR120" s="120"/>
+      <c r="AS120" s="120"/>
     </row>
     <row r="121" spans="1:45" ht="43.8" thickBot="1">
       <c r="A121" s="11" t="s">
@@ -11332,54 +11332,54 @@
       <c r="E138" s="110"/>
     </row>
     <row r="139" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A139" s="119" t="s">
+      <c r="A139" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="B139" s="119"/>
-      <c r="C139" s="119"/>
-      <c r="D139" s="119"/>
-      <c r="E139" s="119"/>
-      <c r="F139" s="119"/>
-      <c r="G139" s="119"/>
-      <c r="H139" s="119"/>
-      <c r="I139" s="119"/>
-      <c r="J139" s="119"/>
-      <c r="K139" s="119"/>
-      <c r="L139" s="119"/>
-      <c r="M139" s="119"/>
-      <c r="N139" s="119"/>
-      <c r="O139" s="119"/>
-      <c r="P139" s="119"/>
-      <c r="Q139" s="119"/>
-      <c r="R139" s="119"/>
-      <c r="S139" s="119"/>
-      <c r="T139" s="119"/>
+      <c r="B139" s="121"/>
+      <c r="C139" s="121"/>
+      <c r="D139" s="121"/>
+      <c r="E139" s="121"/>
+      <c r="F139" s="121"/>
+      <c r="G139" s="121"/>
+      <c r="H139" s="121"/>
+      <c r="I139" s="121"/>
+      <c r="J139" s="121"/>
+      <c r="K139" s="121"/>
+      <c r="L139" s="121"/>
+      <c r="M139" s="121"/>
+      <c r="N139" s="121"/>
+      <c r="O139" s="121"/>
+      <c r="P139" s="121"/>
+      <c r="Q139" s="121"/>
+      <c r="R139" s="121"/>
+      <c r="S139" s="121"/>
+      <c r="T139" s="121"/>
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
       <c r="W139" s="10"/>
       <c r="X139" s="10"/>
       <c r="Y139" s="10"/>
       <c r="Z139" s="10"/>
-      <c r="AA139" s="120"/>
-      <c r="AB139" s="121"/>
+      <c r="AA139" s="117"/>
+      <c r="AB139" s="118"/>
       <c r="AC139" s="103"/>
-      <c r="AE139" s="117" t="s">
+      <c r="AE139" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF139" s="118"/>
-      <c r="AG139" s="118"/>
-      <c r="AH139" s="118"/>
-      <c r="AI139" s="118"/>
-      <c r="AJ139" s="118"/>
-      <c r="AK139" s="118"/>
-      <c r="AL139" s="118"/>
-      <c r="AM139" s="118"/>
-      <c r="AN139" s="118"/>
-      <c r="AO139" s="118"/>
-      <c r="AP139" s="118"/>
-      <c r="AQ139" s="118"/>
-      <c r="AR139" s="118"/>
-      <c r="AS139" s="118"/>
+      <c r="AF139" s="120"/>
+      <c r="AG139" s="120"/>
+      <c r="AH139" s="120"/>
+      <c r="AI139" s="120"/>
+      <c r="AJ139" s="120"/>
+      <c r="AK139" s="120"/>
+      <c r="AL139" s="120"/>
+      <c r="AM139" s="120"/>
+      <c r="AN139" s="120"/>
+      <c r="AO139" s="120"/>
+      <c r="AP139" s="120"/>
+      <c r="AQ139" s="120"/>
+      <c r="AR139" s="120"/>
+      <c r="AS139" s="120"/>
     </row>
     <row r="140" spans="1:45" ht="43.8" thickBot="1">
       <c r="A140" s="11" t="s">
@@ -12567,54 +12567,54 @@
       </c>
     </row>
     <row r="158" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A158" s="119" t="s">
+      <c r="A158" s="121" t="s">
         <v>150</v>
       </c>
-      <c r="B158" s="119"/>
-      <c r="C158" s="119"/>
-      <c r="D158" s="119"/>
-      <c r="E158" s="119"/>
-      <c r="F158" s="119"/>
-      <c r="G158" s="119"/>
-      <c r="H158" s="119"/>
-      <c r="I158" s="119"/>
-      <c r="J158" s="119"/>
-      <c r="K158" s="119"/>
-      <c r="L158" s="119"/>
-      <c r="M158" s="119"/>
-      <c r="N158" s="119"/>
-      <c r="O158" s="119"/>
-      <c r="P158" s="119"/>
-      <c r="Q158" s="119"/>
-      <c r="R158" s="119"/>
-      <c r="S158" s="119"/>
-      <c r="T158" s="119"/>
+      <c r="B158" s="121"/>
+      <c r="C158" s="121"/>
+      <c r="D158" s="121"/>
+      <c r="E158" s="121"/>
+      <c r="F158" s="121"/>
+      <c r="G158" s="121"/>
+      <c r="H158" s="121"/>
+      <c r="I158" s="121"/>
+      <c r="J158" s="121"/>
+      <c r="K158" s="121"/>
+      <c r="L158" s="121"/>
+      <c r="M158" s="121"/>
+      <c r="N158" s="121"/>
+      <c r="O158" s="121"/>
+      <c r="P158" s="121"/>
+      <c r="Q158" s="121"/>
+      <c r="R158" s="121"/>
+      <c r="S158" s="121"/>
+      <c r="T158" s="121"/>
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
       <c r="W158" s="10"/>
       <c r="X158" s="10"/>
       <c r="Y158" s="10"/>
       <c r="Z158" s="10"/>
-      <c r="AA158" s="120"/>
-      <c r="AB158" s="121"/>
+      <c r="AA158" s="117"/>
+      <c r="AB158" s="118"/>
       <c r="AC158" s="103"/>
-      <c r="AE158" s="117" t="s">
+      <c r="AE158" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF158" s="118"/>
-      <c r="AG158" s="118"/>
-      <c r="AH158" s="118"/>
-      <c r="AI158" s="118"/>
-      <c r="AJ158" s="118"/>
-      <c r="AK158" s="118"/>
-      <c r="AL158" s="118"/>
-      <c r="AM158" s="118"/>
-      <c r="AN158" s="118"/>
-      <c r="AO158" s="118"/>
-      <c r="AP158" s="118"/>
-      <c r="AQ158" s="118"/>
-      <c r="AR158" s="118"/>
-      <c r="AS158" s="118"/>
+      <c r="AF158" s="120"/>
+      <c r="AG158" s="120"/>
+      <c r="AH158" s="120"/>
+      <c r="AI158" s="120"/>
+      <c r="AJ158" s="120"/>
+      <c r="AK158" s="120"/>
+      <c r="AL158" s="120"/>
+      <c r="AM158" s="120"/>
+      <c r="AN158" s="120"/>
+      <c r="AO158" s="120"/>
+      <c r="AP158" s="120"/>
+      <c r="AQ158" s="120"/>
+      <c r="AR158" s="120"/>
+      <c r="AS158" s="120"/>
     </row>
     <row r="159" spans="1:45" ht="43.8" thickBot="1">
       <c r="A159" s="11" t="s">
@@ -13763,54 +13763,54 @@
       </c>
     </row>
     <row r="174" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A174" s="119" t="s">
+      <c r="A174" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="B174" s="119"/>
-      <c r="C174" s="119"/>
-      <c r="D174" s="119"/>
-      <c r="E174" s="119"/>
-      <c r="F174" s="119"/>
-      <c r="G174" s="119"/>
-      <c r="H174" s="119"/>
-      <c r="I174" s="119"/>
-      <c r="J174" s="119"/>
-      <c r="K174" s="119"/>
-      <c r="L174" s="119"/>
-      <c r="M174" s="119"/>
-      <c r="N174" s="119"/>
-      <c r="O174" s="119"/>
-      <c r="P174" s="119"/>
-      <c r="Q174" s="119"/>
-      <c r="R174" s="119"/>
-      <c r="S174" s="119"/>
-      <c r="T174" s="119"/>
+      <c r="B174" s="121"/>
+      <c r="C174" s="121"/>
+      <c r="D174" s="121"/>
+      <c r="E174" s="121"/>
+      <c r="F174" s="121"/>
+      <c r="G174" s="121"/>
+      <c r="H174" s="121"/>
+      <c r="I174" s="121"/>
+      <c r="J174" s="121"/>
+      <c r="K174" s="121"/>
+      <c r="L174" s="121"/>
+      <c r="M174" s="121"/>
+      <c r="N174" s="121"/>
+      <c r="O174" s="121"/>
+      <c r="P174" s="121"/>
+      <c r="Q174" s="121"/>
+      <c r="R174" s="121"/>
+      <c r="S174" s="121"/>
+      <c r="T174" s="121"/>
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
       <c r="W174" s="10"/>
       <c r="X174" s="10"/>
       <c r="Y174" s="10"/>
       <c r="Z174" s="10"/>
-      <c r="AA174" s="120"/>
-      <c r="AB174" s="121"/>
+      <c r="AA174" s="117"/>
+      <c r="AB174" s="118"/>
       <c r="AC174" s="103"/>
-      <c r="AE174" s="117" t="s">
+      <c r="AE174" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF174" s="118"/>
-      <c r="AG174" s="118"/>
-      <c r="AH174" s="118"/>
-      <c r="AI174" s="118"/>
-      <c r="AJ174" s="118"/>
-      <c r="AK174" s="118"/>
-      <c r="AL174" s="118"/>
-      <c r="AM174" s="118"/>
-      <c r="AN174" s="118"/>
-      <c r="AO174" s="118"/>
-      <c r="AP174" s="118"/>
-      <c r="AQ174" s="118"/>
-      <c r="AR174" s="118"/>
-      <c r="AS174" s="118"/>
+      <c r="AF174" s="120"/>
+      <c r="AG174" s="120"/>
+      <c r="AH174" s="120"/>
+      <c r="AI174" s="120"/>
+      <c r="AJ174" s="120"/>
+      <c r="AK174" s="120"/>
+      <c r="AL174" s="120"/>
+      <c r="AM174" s="120"/>
+      <c r="AN174" s="120"/>
+      <c r="AO174" s="120"/>
+      <c r="AP174" s="120"/>
+      <c r="AQ174" s="120"/>
+      <c r="AR174" s="120"/>
+      <c r="AS174" s="120"/>
     </row>
     <row r="175" spans="1:45" ht="43.8" thickBot="1">
       <c r="A175" s="11" t="s">
@@ -14894,7 +14894,7 @@
         <v>33</v>
       </c>
       <c r="J188" s="60">
-        <f>SUM(G182:V182)-AE180</f>
+        <f>SUM(G182:V182)</f>
         <v>2194998.23</v>
       </c>
       <c r="L188" s="67" t="s">
@@ -14963,54 +14963,54 @@
       </c>
     </row>
     <row r="192" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A192" s="119" t="s">
+      <c r="A192" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="B192" s="119"/>
-      <c r="C192" s="119"/>
-      <c r="D192" s="119"/>
-      <c r="E192" s="119"/>
-      <c r="F192" s="119"/>
-      <c r="G192" s="119"/>
-      <c r="H192" s="119"/>
-      <c r="I192" s="119"/>
-      <c r="J192" s="119"/>
-      <c r="K192" s="119"/>
-      <c r="L192" s="119"/>
-      <c r="M192" s="119"/>
-      <c r="N192" s="119"/>
-      <c r="O192" s="119"/>
-      <c r="P192" s="119"/>
-      <c r="Q192" s="119"/>
-      <c r="R192" s="119"/>
-      <c r="S192" s="119"/>
-      <c r="T192" s="119"/>
+      <c r="B192" s="121"/>
+      <c r="C192" s="121"/>
+      <c r="D192" s="121"/>
+      <c r="E192" s="121"/>
+      <c r="F192" s="121"/>
+      <c r="G192" s="121"/>
+      <c r="H192" s="121"/>
+      <c r="I192" s="121"/>
+      <c r="J192" s="121"/>
+      <c r="K192" s="121"/>
+      <c r="L192" s="121"/>
+      <c r="M192" s="121"/>
+      <c r="N192" s="121"/>
+      <c r="O192" s="121"/>
+      <c r="P192" s="121"/>
+      <c r="Q192" s="121"/>
+      <c r="R192" s="121"/>
+      <c r="S192" s="121"/>
+      <c r="T192" s="121"/>
       <c r="U192" s="10"/>
       <c r="V192" s="10"/>
       <c r="W192" s="10"/>
       <c r="X192" s="10"/>
       <c r="Y192" s="10"/>
       <c r="Z192" s="10"/>
-      <c r="AA192" s="120"/>
-      <c r="AB192" s="121"/>
+      <c r="AA192" s="117"/>
+      <c r="AB192" s="118"/>
       <c r="AC192" s="103"/>
-      <c r="AE192" s="117" t="s">
+      <c r="AE192" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="AF192" s="118"/>
-      <c r="AG192" s="118"/>
-      <c r="AH192" s="118"/>
-      <c r="AI192" s="118"/>
-      <c r="AJ192" s="118"/>
-      <c r="AK192" s="118"/>
-      <c r="AL192" s="118"/>
-      <c r="AM192" s="118"/>
-      <c r="AN192" s="118"/>
-      <c r="AO192" s="118"/>
-      <c r="AP192" s="118"/>
-      <c r="AQ192" s="118"/>
-      <c r="AR192" s="118"/>
-      <c r="AS192" s="118"/>
+      <c r="AF192" s="120"/>
+      <c r="AG192" s="120"/>
+      <c r="AH192" s="120"/>
+      <c r="AI192" s="120"/>
+      <c r="AJ192" s="120"/>
+      <c r="AK192" s="120"/>
+      <c r="AL192" s="120"/>
+      <c r="AM192" s="120"/>
+      <c r="AN192" s="120"/>
+      <c r="AO192" s="120"/>
+      <c r="AP192" s="120"/>
+      <c r="AQ192" s="120"/>
+      <c r="AR192" s="120"/>
+      <c r="AS192" s="120"/>
     </row>
     <row r="193" spans="1:45" ht="43.8" thickBot="1">
       <c r="A193" s="11" t="s">
@@ -16126,15 +16126,15 @@
         <v>33</v>
       </c>
       <c r="J206" s="60">
-        <f>SUM(G200:V200)-AD204</f>
-        <v>1892796.6999999997</v>
+        <f>SUM(G200:V200)</f>
+        <v>1939076.6999999997</v>
       </c>
       <c r="L206" s="67" t="s">
         <v>77</v>
       </c>
       <c r="M206" s="68">
         <f>(G206-J206)</f>
-        <v>46280.160000000615</v>
+        <v>0.1600000006146729</v>
       </c>
       <c r="O206" s="61" t="s">
         <v>95</v>
@@ -16192,34 +16192,42 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="AA192:AB192"/>
-    <mergeCell ref="AE192:AS192"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="E192:H192"/>
-    <mergeCell ref="I192:L192"/>
-    <mergeCell ref="M192:P192"/>
-    <mergeCell ref="Q192:T192"/>
-    <mergeCell ref="AA174:AB174"/>
-    <mergeCell ref="AE174:AS174"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="E174:H174"/>
-    <mergeCell ref="I174:L174"/>
-    <mergeCell ref="M174:P174"/>
-    <mergeCell ref="Q174:T174"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="A158:D158"/>
-    <mergeCell ref="AE158:AS158"/>
-    <mergeCell ref="AA158:AB158"/>
-    <mergeCell ref="Q158:T158"/>
-    <mergeCell ref="M158:P158"/>
-    <mergeCell ref="I158:L158"/>
-    <mergeCell ref="AA139:AB139"/>
-    <mergeCell ref="AE139:AS139"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="M139:P139"/>
-    <mergeCell ref="Q139:T139"/>
+    <mergeCell ref="AE103:AS103"/>
+    <mergeCell ref="AE120:AS120"/>
+    <mergeCell ref="AE37:AS37"/>
+    <mergeCell ref="AE54:AS54"/>
+    <mergeCell ref="AE69:AS69"/>
+    <mergeCell ref="AE87:AS87"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="M103:P103"/>
+    <mergeCell ref="Q103:T103"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q54:T54"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="M87:P87"/>
+    <mergeCell ref="Q87:T87"/>
     <mergeCell ref="AA120:AB120"/>
     <mergeCell ref="AE2:AS2"/>
     <mergeCell ref="AE21:AS21"/>
@@ -16236,42 +16244,34 @@
     <mergeCell ref="I69:L69"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="M87:P87"/>
-    <mergeCell ref="Q87:T87"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q54:T54"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="M103:P103"/>
-    <mergeCell ref="Q103:T103"/>
-    <mergeCell ref="AE103:AS103"/>
-    <mergeCell ref="AE120:AS120"/>
-    <mergeCell ref="AE37:AS37"/>
-    <mergeCell ref="AE54:AS54"/>
-    <mergeCell ref="AE69:AS69"/>
-    <mergeCell ref="AE87:AS87"/>
+    <mergeCell ref="AA139:AB139"/>
+    <mergeCell ref="AE139:AS139"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="M139:P139"/>
+    <mergeCell ref="Q139:T139"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="AE158:AS158"/>
+    <mergeCell ref="AA158:AB158"/>
+    <mergeCell ref="Q158:T158"/>
+    <mergeCell ref="M158:P158"/>
+    <mergeCell ref="I158:L158"/>
+    <mergeCell ref="AA174:AB174"/>
+    <mergeCell ref="AE174:AS174"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="E174:H174"/>
+    <mergeCell ref="I174:L174"/>
+    <mergeCell ref="M174:P174"/>
+    <mergeCell ref="Q174:T174"/>
+    <mergeCell ref="AA192:AB192"/>
+    <mergeCell ref="AE192:AS192"/>
+    <mergeCell ref="A192:D192"/>
+    <mergeCell ref="E192:H192"/>
+    <mergeCell ref="I192:L192"/>
+    <mergeCell ref="M192:P192"/>
+    <mergeCell ref="Q192:T192"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Zen_Estate_Combined_Expenses_Q1.xlsx
+++ b/Zen_Estate_Combined_Expenses_Q1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 13\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhootm\Desktop\Zen Estate\working data new 14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4046F2F7-4C93-4B87-9261-37D56365D0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90555470-5BBA-481E-805F-3D3FDDEE8142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1590,6 +1590,9 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1619,9 +1622,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1983,51 +1983,51 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="78"/>
       <c r="Z2" s="69"/>
-      <c r="AE2" s="121" t="s">
+      <c r="AE2" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
-      <c r="AH2" s="122"/>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="122"/>
-      <c r="AO2" s="122"/>
-      <c r="AP2" s="122"/>
-      <c r="AQ2" s="122"/>
-      <c r="AR2" s="122"/>
-      <c r="AS2" s="122"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
+      <c r="AH2" s="123"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="123"/>
+      <c r="AL2" s="123"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="123"/>
+      <c r="AO2" s="123"/>
+      <c r="AP2" s="123"/>
+      <c r="AQ2" s="123"/>
+      <c r="AR2" s="123"/>
+      <c r="AS2" s="123"/>
     </row>
     <row r="3" spans="1:45" ht="15" thickBot="1">
       <c r="A3" s="8" t="s">
@@ -3155,51 +3155,51 @@
       </c>
     </row>
     <row r="21" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A21" s="120" t="s">
+      <c r="A21" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="120"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="120"/>
-      <c r="L21" s="120"/>
-      <c r="M21" s="120"/>
-      <c r="N21" s="120"/>
-      <c r="O21" s="120"/>
-      <c r="P21" s="120"/>
-      <c r="Q21" s="120"/>
-      <c r="R21" s="120"/>
-      <c r="S21" s="120"/>
-      <c r="T21" s="120"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="121"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="78"/>
       <c r="Z21" s="69"/>
-      <c r="AE21" s="121" t="s">
+      <c r="AE21" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="AF21" s="122"/>
-      <c r="AG21" s="122"/>
-      <c r="AH21" s="122"/>
-      <c r="AI21" s="122"/>
-      <c r="AJ21" s="122"/>
-      <c r="AK21" s="122"/>
-      <c r="AL21" s="122"/>
-      <c r="AM21" s="122"/>
-      <c r="AN21" s="122"/>
-      <c r="AO21" s="122"/>
-      <c r="AP21" s="122"/>
-      <c r="AQ21" s="122"/>
-      <c r="AR21" s="122"/>
-      <c r="AS21" s="122"/>
+      <c r="AF21" s="123"/>
+      <c r="AG21" s="123"/>
+      <c r="AH21" s="123"/>
+      <c r="AI21" s="123"/>
+      <c r="AJ21" s="123"/>
+      <c r="AK21" s="123"/>
+      <c r="AL21" s="123"/>
+      <c r="AM21" s="123"/>
+      <c r="AN21" s="123"/>
+      <c r="AO21" s="123"/>
+      <c r="AP21" s="123"/>
+      <c r="AQ21" s="123"/>
+      <c r="AR21" s="123"/>
+      <c r="AS21" s="123"/>
     </row>
     <row r="22" spans="1:45" ht="15" thickBot="1">
       <c r="A22" s="8" t="s">
@@ -4278,28 +4278,28 @@
       </c>
     </row>
     <row r="37" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A37" s="120" t="s">
+      <c r="A37" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="120"/>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="120"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="120"/>
-      <c r="P37" s="120"/>
-      <c r="Q37" s="120"/>
-      <c r="R37" s="120"/>
-      <c r="S37" s="120"/>
-      <c r="T37" s="120"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="121"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
@@ -4309,23 +4309,23 @@
       <c r="AA37" s="31"/>
       <c r="AB37" s="31"/>
       <c r="AC37" s="31"/>
-      <c r="AE37" s="117" t="s">
+      <c r="AE37" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF37" s="118"/>
-      <c r="AG37" s="118"/>
-      <c r="AH37" s="118"/>
-      <c r="AI37" s="118"/>
-      <c r="AJ37" s="118"/>
-      <c r="AK37" s="118"/>
-      <c r="AL37" s="118"/>
-      <c r="AM37" s="118"/>
-      <c r="AN37" s="118"/>
-      <c r="AO37" s="118"/>
-      <c r="AP37" s="118"/>
-      <c r="AQ37" s="118"/>
-      <c r="AR37" s="118"/>
-      <c r="AS37" s="118"/>
+      <c r="AF37" s="119"/>
+      <c r="AG37" s="119"/>
+      <c r="AH37" s="119"/>
+      <c r="AI37" s="119"/>
+      <c r="AJ37" s="119"/>
+      <c r="AK37" s="119"/>
+      <c r="AL37" s="119"/>
+      <c r="AM37" s="119"/>
+      <c r="AN37" s="119"/>
+      <c r="AO37" s="119"/>
+      <c r="AP37" s="119"/>
+      <c r="AQ37" s="119"/>
+      <c r="AR37" s="119"/>
+      <c r="AS37" s="119"/>
     </row>
     <row r="38" spans="1:46" ht="15" thickBot="1">
       <c r="A38" s="8" t="s">
@@ -5446,51 +5446,51 @@
       </c>
     </row>
     <row r="54" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A54" s="120" t="s">
+      <c r="A54" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="120"/>
-      <c r="C54" s="120"/>
-      <c r="D54" s="120"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
-      <c r="H54" s="120"/>
-      <c r="I54" s="120"/>
-      <c r="J54" s="120"/>
-      <c r="K54" s="120"/>
-      <c r="L54" s="120"/>
-      <c r="M54" s="120"/>
-      <c r="N54" s="120"/>
-      <c r="O54" s="120"/>
-      <c r="P54" s="120"/>
-      <c r="Q54" s="120"/>
-      <c r="R54" s="120"/>
-      <c r="S54" s="120"/>
-      <c r="T54" s="120"/>
+      <c r="B54" s="121"/>
+      <c r="C54" s="121"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="121"/>
+      <c r="I54" s="121"/>
+      <c r="J54" s="121"/>
+      <c r="K54" s="121"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="121"/>
+      <c r="R54" s="121"/>
+      <c r="S54" s="121"/>
+      <c r="T54" s="121"/>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
       <c r="W54" s="7"/>
       <c r="X54" s="78"/>
       <c r="Y54" s="78"/>
       <c r="Z54" s="79"/>
-      <c r="AE54" s="117" t="s">
+      <c r="AE54" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF54" s="118"/>
-      <c r="AG54" s="118"/>
-      <c r="AH54" s="118"/>
-      <c r="AI54" s="118"/>
-      <c r="AJ54" s="118"/>
-      <c r="AK54" s="118"/>
-      <c r="AL54" s="118"/>
-      <c r="AM54" s="118"/>
-      <c r="AN54" s="118"/>
-      <c r="AO54" s="118"/>
-      <c r="AP54" s="118"/>
-      <c r="AQ54" s="118"/>
-      <c r="AR54" s="118"/>
-      <c r="AS54" s="118"/>
+      <c r="AF54" s="119"/>
+      <c r="AG54" s="119"/>
+      <c r="AH54" s="119"/>
+      <c r="AI54" s="119"/>
+      <c r="AJ54" s="119"/>
+      <c r="AK54" s="119"/>
+      <c r="AL54" s="119"/>
+      <c r="AM54" s="119"/>
+      <c r="AN54" s="119"/>
+      <c r="AO54" s="119"/>
+      <c r="AP54" s="119"/>
+      <c r="AQ54" s="119"/>
+      <c r="AR54" s="119"/>
+      <c r="AS54" s="119"/>
     </row>
     <row r="55" spans="1:46" ht="15" thickBot="1">
       <c r="A55" s="8" t="s">
@@ -6566,54 +6566,54 @@
       <c r="V68" s="17"/>
     </row>
     <row r="69" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A69" s="120" t="s">
+      <c r="A69" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="120"/>
-      <c r="C69" s="120"/>
-      <c r="D69" s="120"/>
-      <c r="E69" s="120"/>
-      <c r="F69" s="120"/>
-      <c r="G69" s="120"/>
-      <c r="H69" s="120"/>
-      <c r="I69" s="120"/>
-      <c r="J69" s="120"/>
-      <c r="K69" s="120"/>
-      <c r="L69" s="120"/>
-      <c r="M69" s="120"/>
-      <c r="N69" s="120"/>
-      <c r="O69" s="120"/>
-      <c r="P69" s="120"/>
-      <c r="Q69" s="120"/>
-      <c r="R69" s="120"/>
-      <c r="S69" s="120"/>
-      <c r="T69" s="120"/>
+      <c r="B69" s="121"/>
+      <c r="C69" s="121"/>
+      <c r="D69" s="121"/>
+      <c r="E69" s="121"/>
+      <c r="F69" s="121"/>
+      <c r="G69" s="121"/>
+      <c r="H69" s="121"/>
+      <c r="I69" s="121"/>
+      <c r="J69" s="121"/>
+      <c r="K69" s="121"/>
+      <c r="L69" s="121"/>
+      <c r="M69" s="121"/>
+      <c r="N69" s="121"/>
+      <c r="O69" s="121"/>
+      <c r="P69" s="121"/>
+      <c r="Q69" s="121"/>
+      <c r="R69" s="121"/>
+      <c r="S69" s="121"/>
+      <c r="T69" s="121"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
-      <c r="AA69" s="115"/>
-      <c r="AB69" s="116"/>
+      <c r="AA69" s="116"/>
+      <c r="AB69" s="117"/>
       <c r="AC69" s="97"/>
-      <c r="AE69" s="117" t="s">
+      <c r="AE69" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF69" s="118"/>
-      <c r="AG69" s="118"/>
-      <c r="AH69" s="118"/>
-      <c r="AI69" s="118"/>
-      <c r="AJ69" s="118"/>
-      <c r="AK69" s="118"/>
-      <c r="AL69" s="118"/>
-      <c r="AM69" s="118"/>
-      <c r="AN69" s="118"/>
-      <c r="AO69" s="118"/>
-      <c r="AP69" s="118"/>
-      <c r="AQ69" s="118"/>
-      <c r="AR69" s="118"/>
-      <c r="AS69" s="118"/>
+      <c r="AF69" s="119"/>
+      <c r="AG69" s="119"/>
+      <c r="AH69" s="119"/>
+      <c r="AI69" s="119"/>
+      <c r="AJ69" s="119"/>
+      <c r="AK69" s="119"/>
+      <c r="AL69" s="119"/>
+      <c r="AM69" s="119"/>
+      <c r="AN69" s="119"/>
+      <c r="AO69" s="119"/>
+      <c r="AP69" s="119"/>
+      <c r="AQ69" s="119"/>
+      <c r="AR69" s="119"/>
+      <c r="AS69" s="119"/>
     </row>
     <row r="70" spans="1:45" ht="43.8" thickBot="1">
       <c r="A70" s="8" t="s">
@@ -7737,54 +7737,54 @@
       </c>
     </row>
     <row r="87" spans="1:46" ht="18.600000000000001" thickBot="1">
-      <c r="A87" s="120" t="s">
+      <c r="A87" s="121" t="s">
         <v>106</v>
       </c>
-      <c r="B87" s="120"/>
-      <c r="C87" s="120"/>
-      <c r="D87" s="120"/>
-      <c r="E87" s="120"/>
-      <c r="F87" s="120"/>
-      <c r="G87" s="120"/>
-      <c r="H87" s="120"/>
-      <c r="I87" s="120"/>
-      <c r="J87" s="120"/>
-      <c r="K87" s="120"/>
-      <c r="L87" s="120"/>
-      <c r="M87" s="120"/>
-      <c r="N87" s="120"/>
-      <c r="O87" s="120"/>
-      <c r="P87" s="120"/>
-      <c r="Q87" s="120"/>
-      <c r="R87" s="120"/>
-      <c r="S87" s="120"/>
-      <c r="T87" s="120"/>
+      <c r="B87" s="121"/>
+      <c r="C87" s="121"/>
+      <c r="D87" s="121"/>
+      <c r="E87" s="121"/>
+      <c r="F87" s="121"/>
+      <c r="G87" s="121"/>
+      <c r="H87" s="121"/>
+      <c r="I87" s="121"/>
+      <c r="J87" s="121"/>
+      <c r="K87" s="121"/>
+      <c r="L87" s="121"/>
+      <c r="M87" s="121"/>
+      <c r="N87" s="121"/>
+      <c r="O87" s="121"/>
+      <c r="P87" s="121"/>
+      <c r="Q87" s="121"/>
+      <c r="R87" s="121"/>
+      <c r="S87" s="121"/>
+      <c r="T87" s="121"/>
       <c r="U87" s="7"/>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
-      <c r="AA87" s="115"/>
-      <c r="AB87" s="116"/>
+      <c r="AA87" s="116"/>
+      <c r="AB87" s="117"/>
       <c r="AC87" s="97"/>
-      <c r="AE87" s="117" t="s">
+      <c r="AE87" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF87" s="118"/>
-      <c r="AG87" s="118"/>
-      <c r="AH87" s="118"/>
-      <c r="AI87" s="118"/>
-      <c r="AJ87" s="118"/>
-      <c r="AK87" s="118"/>
-      <c r="AL87" s="118"/>
-      <c r="AM87" s="118"/>
-      <c r="AN87" s="118"/>
-      <c r="AO87" s="118"/>
-      <c r="AP87" s="118"/>
-      <c r="AQ87" s="118"/>
-      <c r="AR87" s="118"/>
-      <c r="AS87" s="118"/>
+      <c r="AF87" s="119"/>
+      <c r="AG87" s="119"/>
+      <c r="AH87" s="119"/>
+      <c r="AI87" s="119"/>
+      <c r="AJ87" s="119"/>
+      <c r="AK87" s="119"/>
+      <c r="AL87" s="119"/>
+      <c r="AM87" s="119"/>
+      <c r="AN87" s="119"/>
+      <c r="AO87" s="119"/>
+      <c r="AP87" s="119"/>
+      <c r="AQ87" s="119"/>
+      <c r="AR87" s="119"/>
+      <c r="AS87" s="119"/>
     </row>
     <row r="88" spans="1:46" ht="43.8" thickBot="1">
       <c r="A88" s="8" t="s">
@@ -8927,54 +8927,54 @@
       </c>
     </row>
     <row r="103" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A103" s="120" t="s">
+      <c r="A103" s="121" t="s">
         <v>110</v>
       </c>
-      <c r="B103" s="120"/>
-      <c r="C103" s="120"/>
-      <c r="D103" s="120"/>
-      <c r="E103" s="120"/>
-      <c r="F103" s="120"/>
-      <c r="G103" s="120"/>
-      <c r="H103" s="120"/>
-      <c r="I103" s="120"/>
-      <c r="J103" s="120"/>
-      <c r="K103" s="120"/>
-      <c r="L103" s="120"/>
-      <c r="M103" s="120"/>
-      <c r="N103" s="120"/>
-      <c r="O103" s="120"/>
-      <c r="P103" s="120"/>
-      <c r="Q103" s="120"/>
-      <c r="R103" s="120"/>
-      <c r="S103" s="120"/>
-      <c r="T103" s="120"/>
+      <c r="B103" s="121"/>
+      <c r="C103" s="121"/>
+      <c r="D103" s="121"/>
+      <c r="E103" s="121"/>
+      <c r="F103" s="121"/>
+      <c r="G103" s="121"/>
+      <c r="H103" s="121"/>
+      <c r="I103" s="121"/>
+      <c r="J103" s="121"/>
+      <c r="K103" s="121"/>
+      <c r="L103" s="121"/>
+      <c r="M103" s="121"/>
+      <c r="N103" s="121"/>
+      <c r="O103" s="121"/>
+      <c r="P103" s="121"/>
+      <c r="Q103" s="121"/>
+      <c r="R103" s="121"/>
+      <c r="S103" s="121"/>
+      <c r="T103" s="121"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7"/>
       <c r="W103" s="7"/>
       <c r="X103" s="7"/>
       <c r="Y103" s="7"/>
       <c r="Z103" s="7"/>
-      <c r="AA103" s="115"/>
-      <c r="AB103" s="116"/>
+      <c r="AA103" s="116"/>
+      <c r="AB103" s="117"/>
       <c r="AC103" s="97"/>
-      <c r="AE103" s="117" t="s">
+      <c r="AE103" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF103" s="118"/>
-      <c r="AG103" s="118"/>
-      <c r="AH103" s="118"/>
-      <c r="AI103" s="118"/>
-      <c r="AJ103" s="118"/>
-      <c r="AK103" s="118"/>
-      <c r="AL103" s="118"/>
-      <c r="AM103" s="118"/>
-      <c r="AN103" s="118"/>
-      <c r="AO103" s="118"/>
-      <c r="AP103" s="118"/>
-      <c r="AQ103" s="118"/>
-      <c r="AR103" s="118"/>
-      <c r="AS103" s="118"/>
+      <c r="AF103" s="119"/>
+      <c r="AG103" s="119"/>
+      <c r="AH103" s="119"/>
+      <c r="AI103" s="119"/>
+      <c r="AJ103" s="119"/>
+      <c r="AK103" s="119"/>
+      <c r="AL103" s="119"/>
+      <c r="AM103" s="119"/>
+      <c r="AN103" s="119"/>
+      <c r="AO103" s="119"/>
+      <c r="AP103" s="119"/>
+      <c r="AQ103" s="119"/>
+      <c r="AR103" s="119"/>
+      <c r="AS103" s="119"/>
     </row>
     <row r="104" spans="1:45" ht="43.8" thickBot="1">
       <c r="A104" s="8" t="s">
@@ -10121,54 +10121,54 @@
       </c>
     </row>
     <row r="120" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A120" s="120" t="s">
+      <c r="A120" s="121" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="120"/>
-      <c r="C120" s="120"/>
-      <c r="D120" s="120"/>
-      <c r="E120" s="120"/>
-      <c r="F120" s="120"/>
-      <c r="G120" s="120"/>
-      <c r="H120" s="120"/>
-      <c r="I120" s="120"/>
-      <c r="J120" s="120"/>
-      <c r="K120" s="120"/>
-      <c r="L120" s="120"/>
-      <c r="M120" s="120"/>
-      <c r="N120" s="120"/>
-      <c r="O120" s="120"/>
-      <c r="P120" s="120"/>
-      <c r="Q120" s="120"/>
-      <c r="R120" s="120"/>
-      <c r="S120" s="120"/>
-      <c r="T120" s="120"/>
+      <c r="B120" s="121"/>
+      <c r="C120" s="121"/>
+      <c r="D120" s="121"/>
+      <c r="E120" s="121"/>
+      <c r="F120" s="121"/>
+      <c r="G120" s="121"/>
+      <c r="H120" s="121"/>
+      <c r="I120" s="121"/>
+      <c r="J120" s="121"/>
+      <c r="K120" s="121"/>
+      <c r="L120" s="121"/>
+      <c r="M120" s="121"/>
+      <c r="N120" s="121"/>
+      <c r="O120" s="121"/>
+      <c r="P120" s="121"/>
+      <c r="Q120" s="121"/>
+      <c r="R120" s="121"/>
+      <c r="S120" s="121"/>
+      <c r="T120" s="121"/>
       <c r="U120" s="7"/>
       <c r="V120" s="7"/>
       <c r="W120" s="7"/>
       <c r="X120" s="7"/>
       <c r="Y120" s="7"/>
       <c r="Z120" s="7"/>
-      <c r="AA120" s="115"/>
-      <c r="AB120" s="116"/>
+      <c r="AA120" s="116"/>
+      <c r="AB120" s="117"/>
       <c r="AC120" s="97"/>
-      <c r="AE120" s="117" t="s">
+      <c r="AE120" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF120" s="118"/>
-      <c r="AG120" s="118"/>
-      <c r="AH120" s="118"/>
-      <c r="AI120" s="118"/>
-      <c r="AJ120" s="118"/>
-      <c r="AK120" s="118"/>
-      <c r="AL120" s="118"/>
-      <c r="AM120" s="118"/>
-      <c r="AN120" s="118"/>
-      <c r="AO120" s="118"/>
-      <c r="AP120" s="118"/>
-      <c r="AQ120" s="118"/>
-      <c r="AR120" s="118"/>
-      <c r="AS120" s="118"/>
+      <c r="AF120" s="119"/>
+      <c r="AG120" s="119"/>
+      <c r="AH120" s="119"/>
+      <c r="AI120" s="119"/>
+      <c r="AJ120" s="119"/>
+      <c r="AK120" s="119"/>
+      <c r="AL120" s="119"/>
+      <c r="AM120" s="119"/>
+      <c r="AN120" s="119"/>
+      <c r="AO120" s="119"/>
+      <c r="AP120" s="119"/>
+      <c r="AQ120" s="119"/>
+      <c r="AR120" s="119"/>
+      <c r="AS120" s="119"/>
     </row>
     <row r="121" spans="1:45" ht="43.8" thickBot="1">
       <c r="A121" s="8" t="s">
@@ -11360,54 +11360,54 @@
       <c r="E138" s="104"/>
     </row>
     <row r="139" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A139" s="120" t="s">
+      <c r="A139" s="121" t="s">
         <v>137</v>
       </c>
-      <c r="B139" s="120"/>
-      <c r="C139" s="120"/>
-      <c r="D139" s="120"/>
-      <c r="E139" s="120"/>
-      <c r="F139" s="120"/>
-      <c r="G139" s="120"/>
-      <c r="H139" s="120"/>
-      <c r="I139" s="120"/>
-      <c r="J139" s="120"/>
-      <c r="K139" s="120"/>
-      <c r="L139" s="120"/>
-      <c r="M139" s="120"/>
-      <c r="N139" s="120"/>
-      <c r="O139" s="120"/>
-      <c r="P139" s="120"/>
-      <c r="Q139" s="120"/>
-      <c r="R139" s="120"/>
-      <c r="S139" s="120"/>
-      <c r="T139" s="120"/>
+      <c r="B139" s="121"/>
+      <c r="C139" s="121"/>
+      <c r="D139" s="121"/>
+      <c r="E139" s="121"/>
+      <c r="F139" s="121"/>
+      <c r="G139" s="121"/>
+      <c r="H139" s="121"/>
+      <c r="I139" s="121"/>
+      <c r="J139" s="121"/>
+      <c r="K139" s="121"/>
+      <c r="L139" s="121"/>
+      <c r="M139" s="121"/>
+      <c r="N139" s="121"/>
+      <c r="O139" s="121"/>
+      <c r="P139" s="121"/>
+      <c r="Q139" s="121"/>
+      <c r="R139" s="121"/>
+      <c r="S139" s="121"/>
+      <c r="T139" s="121"/>
       <c r="U139" s="7"/>
       <c r="V139" s="7"/>
       <c r="W139" s="7"/>
       <c r="X139" s="7"/>
       <c r="Y139" s="7"/>
       <c r="Z139" s="7"/>
-      <c r="AA139" s="115"/>
-      <c r="AB139" s="116"/>
+      <c r="AA139" s="116"/>
+      <c r="AB139" s="117"/>
       <c r="AC139" s="97"/>
-      <c r="AE139" s="117" t="s">
+      <c r="AE139" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF139" s="118"/>
-      <c r="AG139" s="118"/>
-      <c r="AH139" s="118"/>
-      <c r="AI139" s="118"/>
-      <c r="AJ139" s="118"/>
-      <c r="AK139" s="118"/>
-      <c r="AL139" s="118"/>
-      <c r="AM139" s="118"/>
-      <c r="AN139" s="118"/>
-      <c r="AO139" s="118"/>
-      <c r="AP139" s="118"/>
-      <c r="AQ139" s="118"/>
-      <c r="AR139" s="118"/>
-      <c r="AS139" s="118"/>
+      <c r="AF139" s="119"/>
+      <c r="AG139" s="119"/>
+      <c r="AH139" s="119"/>
+      <c r="AI139" s="119"/>
+      <c r="AJ139" s="119"/>
+      <c r="AK139" s="119"/>
+      <c r="AL139" s="119"/>
+      <c r="AM139" s="119"/>
+      <c r="AN139" s="119"/>
+      <c r="AO139" s="119"/>
+      <c r="AP139" s="119"/>
+      <c r="AQ139" s="119"/>
+      <c r="AR139" s="119"/>
+      <c r="AS139" s="119"/>
     </row>
     <row r="140" spans="1:45" ht="43.8" thickBot="1">
       <c r="A140" s="8" t="s">
@@ -12595,54 +12595,54 @@
       </c>
     </row>
     <row r="158" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A158" s="120" t="s">
+      <c r="A158" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="B158" s="120"/>
-      <c r="C158" s="120"/>
-      <c r="D158" s="120"/>
-      <c r="E158" s="120"/>
-      <c r="F158" s="120"/>
-      <c r="G158" s="120"/>
-      <c r="H158" s="120"/>
-      <c r="I158" s="120"/>
-      <c r="J158" s="120"/>
-      <c r="K158" s="120"/>
-      <c r="L158" s="120"/>
-      <c r="M158" s="120"/>
-      <c r="N158" s="120"/>
-      <c r="O158" s="120"/>
-      <c r="P158" s="120"/>
-      <c r="Q158" s="120"/>
-      <c r="R158" s="120"/>
-      <c r="S158" s="120"/>
-      <c r="T158" s="120"/>
+      <c r="B158" s="121"/>
+      <c r="C158" s="121"/>
+      <c r="D158" s="121"/>
+      <c r="E158" s="121"/>
+      <c r="F158" s="121"/>
+      <c r="G158" s="121"/>
+      <c r="H158" s="121"/>
+      <c r="I158" s="121"/>
+      <c r="J158" s="121"/>
+      <c r="K158" s="121"/>
+      <c r="L158" s="121"/>
+      <c r="M158" s="121"/>
+      <c r="N158" s="121"/>
+      <c r="O158" s="121"/>
+      <c r="P158" s="121"/>
+      <c r="Q158" s="121"/>
+      <c r="R158" s="121"/>
+      <c r="S158" s="121"/>
+      <c r="T158" s="121"/>
       <c r="U158" s="7"/>
       <c r="V158" s="7"/>
       <c r="W158" s="7"/>
       <c r="X158" s="7"/>
       <c r="Y158" s="7"/>
       <c r="Z158" s="7"/>
-      <c r="AA158" s="115"/>
-      <c r="AB158" s="116"/>
+      <c r="AA158" s="116"/>
+      <c r="AB158" s="117"/>
       <c r="AC158" s="97"/>
-      <c r="AE158" s="117" t="s">
+      <c r="AE158" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF158" s="118"/>
-      <c r="AG158" s="118"/>
-      <c r="AH158" s="118"/>
-      <c r="AI158" s="118"/>
-      <c r="AJ158" s="118"/>
-      <c r="AK158" s="118"/>
-      <c r="AL158" s="118"/>
-      <c r="AM158" s="118"/>
-      <c r="AN158" s="118"/>
-      <c r="AO158" s="118"/>
-      <c r="AP158" s="118"/>
-      <c r="AQ158" s="118"/>
-      <c r="AR158" s="118"/>
-      <c r="AS158" s="118"/>
+      <c r="AF158" s="119"/>
+      <c r="AG158" s="119"/>
+      <c r="AH158" s="119"/>
+      <c r="AI158" s="119"/>
+      <c r="AJ158" s="119"/>
+      <c r="AK158" s="119"/>
+      <c r="AL158" s="119"/>
+      <c r="AM158" s="119"/>
+      <c r="AN158" s="119"/>
+      <c r="AO158" s="119"/>
+      <c r="AP158" s="119"/>
+      <c r="AQ158" s="119"/>
+      <c r="AR158" s="119"/>
+      <c r="AS158" s="119"/>
     </row>
     <row r="159" spans="1:45" ht="43.8" thickBot="1">
       <c r="A159" s="8" t="s">
@@ -13791,54 +13791,54 @@
       </c>
     </row>
     <row r="174" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A174" s="120" t="s">
+      <c r="A174" s="121" t="s">
         <v>158</v>
       </c>
-      <c r="B174" s="120"/>
-      <c r="C174" s="120"/>
-      <c r="D174" s="120"/>
-      <c r="E174" s="120"/>
-      <c r="F174" s="120"/>
-      <c r="G174" s="120"/>
-      <c r="H174" s="120"/>
-      <c r="I174" s="120"/>
-      <c r="J174" s="120"/>
-      <c r="K174" s="120"/>
-      <c r="L174" s="120"/>
-      <c r="M174" s="120"/>
-      <c r="N174" s="120"/>
-      <c r="O174" s="120"/>
-      <c r="P174" s="120"/>
-      <c r="Q174" s="120"/>
-      <c r="R174" s="120"/>
-      <c r="S174" s="120"/>
-      <c r="T174" s="120"/>
+      <c r="B174" s="121"/>
+      <c r="C174" s="121"/>
+      <c r="D174" s="121"/>
+      <c r="E174" s="121"/>
+      <c r="F174" s="121"/>
+      <c r="G174" s="121"/>
+      <c r="H174" s="121"/>
+      <c r="I174" s="121"/>
+      <c r="J174" s="121"/>
+      <c r="K174" s="121"/>
+      <c r="L174" s="121"/>
+      <c r="M174" s="121"/>
+      <c r="N174" s="121"/>
+      <c r="O174" s="121"/>
+      <c r="P174" s="121"/>
+      <c r="Q174" s="121"/>
+      <c r="R174" s="121"/>
+      <c r="S174" s="121"/>
+      <c r="T174" s="121"/>
       <c r="U174" s="7"/>
       <c r="V174" s="7"/>
       <c r="W174" s="7"/>
       <c r="X174" s="7"/>
       <c r="Y174" s="7"/>
       <c r="Z174" s="7"/>
-      <c r="AA174" s="115"/>
-      <c r="AB174" s="116"/>
+      <c r="AA174" s="116"/>
+      <c r="AB174" s="117"/>
       <c r="AC174" s="97"/>
-      <c r="AE174" s="117" t="s">
+      <c r="AE174" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF174" s="118"/>
-      <c r="AG174" s="118"/>
-      <c r="AH174" s="118"/>
-      <c r="AI174" s="118"/>
-      <c r="AJ174" s="118"/>
-      <c r="AK174" s="118"/>
-      <c r="AL174" s="118"/>
-      <c r="AM174" s="118"/>
-      <c r="AN174" s="118"/>
-      <c r="AO174" s="118"/>
-      <c r="AP174" s="118"/>
-      <c r="AQ174" s="118"/>
-      <c r="AR174" s="118"/>
-      <c r="AS174" s="118"/>
+      <c r="AF174" s="119"/>
+      <c r="AG174" s="119"/>
+      <c r="AH174" s="119"/>
+      <c r="AI174" s="119"/>
+      <c r="AJ174" s="119"/>
+      <c r="AK174" s="119"/>
+      <c r="AL174" s="119"/>
+      <c r="AM174" s="119"/>
+      <c r="AN174" s="119"/>
+      <c r="AO174" s="119"/>
+      <c r="AP174" s="119"/>
+      <c r="AQ174" s="119"/>
+      <c r="AR174" s="119"/>
+      <c r="AS174" s="119"/>
     </row>
     <row r="175" spans="1:45" ht="43.8" thickBot="1">
       <c r="A175" s="8" t="s">
@@ -14991,54 +14991,54 @@
       </c>
     </row>
     <row r="192" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A192" s="120" t="s">
+      <c r="A192" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="B192" s="120"/>
-      <c r="C192" s="120"/>
-      <c r="D192" s="120"/>
-      <c r="E192" s="120"/>
-      <c r="F192" s="120"/>
-      <c r="G192" s="120"/>
-      <c r="H192" s="120"/>
-      <c r="I192" s="120"/>
-      <c r="J192" s="120"/>
-      <c r="K192" s="120"/>
-      <c r="L192" s="120"/>
-      <c r="M192" s="120"/>
-      <c r="N192" s="120"/>
-      <c r="O192" s="120"/>
-      <c r="P192" s="120"/>
-      <c r="Q192" s="120"/>
-      <c r="R192" s="120"/>
-      <c r="S192" s="120"/>
-      <c r="T192" s="120"/>
+      <c r="B192" s="121"/>
+      <c r="C192" s="121"/>
+      <c r="D192" s="121"/>
+      <c r="E192" s="121"/>
+      <c r="F192" s="121"/>
+      <c r="G192" s="121"/>
+      <c r="H192" s="121"/>
+      <c r="I192" s="121"/>
+      <c r="J192" s="121"/>
+      <c r="K192" s="121"/>
+      <c r="L192" s="121"/>
+      <c r="M192" s="121"/>
+      <c r="N192" s="121"/>
+      <c r="O192" s="121"/>
+      <c r="P192" s="121"/>
+      <c r="Q192" s="121"/>
+      <c r="R192" s="121"/>
+      <c r="S192" s="121"/>
+      <c r="T192" s="121"/>
       <c r="U192" s="7"/>
       <c r="V192" s="7"/>
       <c r="W192" s="7"/>
       <c r="X192" s="7"/>
       <c r="Y192" s="7"/>
       <c r="Z192" s="7"/>
-      <c r="AA192" s="115"/>
-      <c r="AB192" s="116"/>
+      <c r="AA192" s="116"/>
+      <c r="AB192" s="117"/>
       <c r="AC192" s="97"/>
-      <c r="AE192" s="117" t="s">
+      <c r="AE192" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF192" s="118"/>
-      <c r="AG192" s="118"/>
-      <c r="AH192" s="118"/>
-      <c r="AI192" s="118"/>
-      <c r="AJ192" s="118"/>
-      <c r="AK192" s="118"/>
-      <c r="AL192" s="118"/>
-      <c r="AM192" s="118"/>
-      <c r="AN192" s="118"/>
-      <c r="AO192" s="118"/>
-      <c r="AP192" s="118"/>
-      <c r="AQ192" s="118"/>
-      <c r="AR192" s="118"/>
-      <c r="AS192" s="118"/>
+      <c r="AF192" s="119"/>
+      <c r="AG192" s="119"/>
+      <c r="AH192" s="119"/>
+      <c r="AI192" s="119"/>
+      <c r="AJ192" s="119"/>
+      <c r="AK192" s="119"/>
+      <c r="AL192" s="119"/>
+      <c r="AM192" s="119"/>
+      <c r="AN192" s="119"/>
+      <c r="AO192" s="119"/>
+      <c r="AP192" s="119"/>
+      <c r="AQ192" s="119"/>
+      <c r="AR192" s="119"/>
+      <c r="AS192" s="119"/>
     </row>
     <row r="193" spans="1:45" ht="43.8" thickBot="1">
       <c r="A193" s="8" t="s">
@@ -16207,54 +16207,54 @@
       </c>
     </row>
     <row r="208" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A208" s="119" t="s">
+      <c r="A208" s="120" t="s">
         <v>199</v>
       </c>
-      <c r="B208" s="120"/>
-      <c r="C208" s="120"/>
-      <c r="D208" s="120"/>
-      <c r="E208" s="120"/>
-      <c r="F208" s="120"/>
-      <c r="G208" s="120"/>
-      <c r="H208" s="120"/>
-      <c r="I208" s="120"/>
-      <c r="J208" s="120"/>
-      <c r="K208" s="120"/>
-      <c r="L208" s="120"/>
-      <c r="M208" s="120"/>
-      <c r="N208" s="120"/>
-      <c r="O208" s="120"/>
-      <c r="P208" s="120"/>
-      <c r="Q208" s="120"/>
-      <c r="R208" s="120"/>
-      <c r="S208" s="120"/>
-      <c r="T208" s="120"/>
+      <c r="B208" s="121"/>
+      <c r="C208" s="121"/>
+      <c r="D208" s="121"/>
+      <c r="E208" s="121"/>
+      <c r="F208" s="121"/>
+      <c r="G208" s="121"/>
+      <c r="H208" s="121"/>
+      <c r="I208" s="121"/>
+      <c r="J208" s="121"/>
+      <c r="K208" s="121"/>
+      <c r="L208" s="121"/>
+      <c r="M208" s="121"/>
+      <c r="N208" s="121"/>
+      <c r="O208" s="121"/>
+      <c r="P208" s="121"/>
+      <c r="Q208" s="121"/>
+      <c r="R208" s="121"/>
+      <c r="S208" s="121"/>
+      <c r="T208" s="121"/>
       <c r="U208" s="7"/>
       <c r="V208" s="7"/>
       <c r="W208" s="7"/>
       <c r="X208" s="7"/>
       <c r="Y208" s="7"/>
       <c r="Z208" s="7"/>
-      <c r="AA208" s="115"/>
-      <c r="AB208" s="116"/>
+      <c r="AA208" s="116"/>
+      <c r="AB208" s="117"/>
       <c r="AC208" s="97"/>
-      <c r="AE208" s="117" t="s">
+      <c r="AE208" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF208" s="118"/>
-      <c r="AG208" s="118"/>
-      <c r="AH208" s="118"/>
-      <c r="AI208" s="118"/>
-      <c r="AJ208" s="118"/>
-      <c r="AK208" s="118"/>
-      <c r="AL208" s="118"/>
-      <c r="AM208" s="118"/>
-      <c r="AN208" s="118"/>
-      <c r="AO208" s="118"/>
-      <c r="AP208" s="118"/>
-      <c r="AQ208" s="118"/>
-      <c r="AR208" s="118"/>
-      <c r="AS208" s="118"/>
+      <c r="AF208" s="119"/>
+      <c r="AG208" s="119"/>
+      <c r="AH208" s="119"/>
+      <c r="AI208" s="119"/>
+      <c r="AJ208" s="119"/>
+      <c r="AK208" s="119"/>
+      <c r="AL208" s="119"/>
+      <c r="AM208" s="119"/>
+      <c r="AN208" s="119"/>
+      <c r="AO208" s="119"/>
+      <c r="AP208" s="119"/>
+      <c r="AQ208" s="119"/>
+      <c r="AR208" s="119"/>
+      <c r="AS208" s="119"/>
     </row>
     <row r="209" spans="1:45" ht="43.8" thickBot="1">
       <c r="A209" s="8" t="s">
@@ -16406,26 +16406,53 @@
       <c r="G210" s="11">
         <v>196874</v>
       </c>
-      <c r="H210" s="12"/>
-      <c r="I210" s="11"/>
-      <c r="J210" s="12"/>
+      <c r="H210" s="12">
+        <v>19530</v>
+      </c>
+      <c r="I210" s="11">
+        <v>194430</v>
+      </c>
+      <c r="J210" s="12">
+        <v>16763.03</v>
+      </c>
       <c r="K210" s="11">
         <v>210430</v>
       </c>
-      <c r="L210" s="11"/>
-      <c r="M210" s="11"/>
-      <c r="N210" s="12"/>
-      <c r="O210" s="11"/>
-      <c r="P210" s="11"/>
-      <c r="Q210" s="11"/>
-      <c r="R210" s="11"/>
+      <c r="L210" s="11">
+        <f>SUM(M210:N210)</f>
+        <v>16763</v>
+      </c>
+      <c r="M210" s="11">
+        <v>13969</v>
+      </c>
+      <c r="N210" s="12">
+        <v>2794</v>
+      </c>
+      <c r="O210" s="11">
+        <v>171577</v>
+      </c>
+      <c r="P210" s="11">
+        <v>16763</v>
+      </c>
+      <c r="Q210" s="11">
+        <v>265618</v>
+      </c>
+      <c r="R210" s="11">
+        <v>22264.41</v>
+      </c>
       <c r="S210" s="11"/>
       <c r="T210" s="11">
         <v>233058.48</v>
       </c>
-      <c r="U210" s="11"/>
-      <c r="V210" s="11"/>
-      <c r="W210" s="72"/>
+      <c r="U210" s="11">
+        <v>206318</v>
+      </c>
+      <c r="V210" s="11">
+        <v>102712</v>
+      </c>
+      <c r="W210" s="72">
+        <v>19530</v>
+      </c>
       <c r="X210" s="74"/>
       <c r="Y210" s="74"/>
       <c r="Z210" s="11">
@@ -16451,7 +16478,9 @@
       <c r="AJ210" s="90"/>
       <c r="AK210" s="90"/>
       <c r="AL210" s="90"/>
-      <c r="AM210" s="90"/>
+      <c r="AM210" s="90">
+        <v>2000</v>
+      </c>
       <c r="AN210" s="90"/>
       <c r="AO210" s="90"/>
       <c r="AP210" s="90"/>
@@ -16490,8 +16519,12 @@
       <c r="S211" s="11"/>
       <c r="T211" s="11"/>
       <c r="U211" s="11"/>
-      <c r="V211" s="11"/>
-      <c r="W211" s="72"/>
+      <c r="V211" s="11">
+        <v>5032.7700000000004</v>
+      </c>
+      <c r="W211" s="72">
+        <v>16763.03</v>
+      </c>
       <c r="X211" s="74"/>
       <c r="Y211" s="89"/>
       <c r="Z211" s="11">
@@ -16515,7 +16548,9 @@
       <c r="AJ211" s="90"/>
       <c r="AK211" s="90"/>
       <c r="AL211" s="90"/>
-      <c r="AM211" s="90"/>
+      <c r="AM211" s="90">
+        <v>2500</v>
+      </c>
       <c r="AN211" s="90"/>
       <c r="AO211" s="90"/>
       <c r="AP211" s="90"/>
@@ -16555,7 +16590,9 @@
       <c r="T212" s="11"/>
       <c r="U212" s="11"/>
       <c r="V212" s="11"/>
-      <c r="W212" s="72"/>
+      <c r="W212" s="72">
+        <v>2794</v>
+      </c>
       <c r="X212" s="74"/>
       <c r="Y212" s="89"/>
       <c r="Z212" s="11"/>
@@ -16567,7 +16604,9 @@
       <c r="AE212" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="AF212" s="90"/>
+      <c r="AF212" s="90">
+        <v>1950</v>
+      </c>
       <c r="AG212" s="90"/>
       <c r="AH212" s="90"/>
       <c r="AI212" s="90"/>
@@ -16687,11 +16726,11 @@
       </c>
       <c r="AE214" s="94">
         <f>SUM(AF214:AS214)</f>
-        <v>0</v>
+        <v>6450</v>
       </c>
       <c r="AF214" s="95">
         <f t="shared" ref="AF214:AG214" si="108">SUM(AF210:AF213)</f>
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="AG214" s="95">
         <f t="shared" si="108"/>
@@ -16719,7 +16758,7 @@
       </c>
       <c r="AM214" s="95">
         <f t="shared" si="109"/>
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="AN214" s="95">
         <f t="shared" si="109"/>
@@ -16808,15 +16847,15 @@
       </c>
       <c r="H216" s="3">
         <f>SUM(H210:H215)</f>
-        <v>0</v>
+        <v>19530</v>
       </c>
       <c r="I216" s="3">
         <f t="shared" ref="I216:L216" si="110">SUM(I210:I215)</f>
-        <v>0</v>
+        <v>194430</v>
       </c>
       <c r="J216" s="3">
         <f t="shared" si="110"/>
-        <v>0</v>
+        <v>16763.03</v>
       </c>
       <c r="K216" s="3">
         <f t="shared" si="110"/>
@@ -16824,25 +16863,25 @@
       </c>
       <c r="L216" s="3">
         <f t="shared" si="110"/>
-        <v>0</v>
+        <v>16763</v>
       </c>
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
       <c r="O216" s="3">
         <f>SUM(O210:O215)</f>
-        <v>0</v>
+        <v>171577</v>
       </c>
       <c r="P216" s="3">
         <f t="shared" ref="P216:V216" si="111">SUM(P210:P215)</f>
-        <v>0</v>
+        <v>16763</v>
       </c>
       <c r="Q216" s="3">
         <f t="shared" si="111"/>
-        <v>0</v>
+        <v>265618</v>
       </c>
       <c r="R216" s="3">
         <f t="shared" si="111"/>
-        <v>0</v>
+        <v>22264.41</v>
       </c>
       <c r="S216" s="3">
         <f t="shared" si="111"/>
@@ -16854,15 +16893,15 @@
       </c>
       <c r="U216" s="3">
         <f t="shared" si="111"/>
-        <v>0</v>
+        <v>206318</v>
       </c>
       <c r="V216" s="3">
         <f t="shared" si="111"/>
-        <v>0</v>
+        <v>107744.77</v>
       </c>
       <c r="W216" s="3">
         <f>SUM(W210:W215)</f>
-        <v>0</v>
+        <v>39087.03</v>
       </c>
       <c r="X216" s="52">
         <f t="shared" ref="X216:AC216" si="112">SUM(X210:X215)</f>
@@ -16979,15 +17018,15 @@
       </c>
       <c r="H218" s="51">
         <f>(H217-H216)</f>
-        <v>19530</v>
+        <v>0</v>
       </c>
       <c r="I218" s="51">
         <f t="shared" ref="I218:L218" si="114">(I217-I216)</f>
-        <v>194430</v>
+        <v>0</v>
       </c>
       <c r="J218" s="51">
         <f t="shared" si="114"/>
-        <v>16763</v>
+        <v>-2.9999999998835847E-2</v>
       </c>
       <c r="K218" s="51">
         <f t="shared" si="114"/>
@@ -16995,25 +17034,25 @@
       </c>
       <c r="L218" s="51">
         <f t="shared" si="114"/>
-        <v>16763</v>
+        <v>0</v>
       </c>
       <c r="M218" s="51"/>
       <c r="N218" s="51"/>
       <c r="O218" s="51">
         <f>(O217-O216)</f>
-        <v>171577</v>
+        <v>0</v>
       </c>
       <c r="P218" s="51">
         <f>(P217-P216)</f>
-        <v>16763</v>
+        <v>0</v>
       </c>
       <c r="Q218" s="51">
         <f t="shared" ref="Q218:R218" si="115">(Q217-Q216)</f>
-        <v>314626</v>
+        <v>49008</v>
       </c>
       <c r="R218" s="51">
         <f t="shared" si="115"/>
-        <v>22264.41</v>
+        <v>0</v>
       </c>
       <c r="S218" s="51">
         <f>(S217-S216)</f>
@@ -17025,11 +17064,11 @@
       </c>
       <c r="U218" s="51">
         <f t="shared" si="116"/>
-        <v>210818.1</v>
+        <v>4500.1000000000058</v>
       </c>
       <c r="V218" s="51">
         <f>(V217-V216)</f>
-        <v>107745.12</v>
+        <v>0.34999999999126885</v>
       </c>
       <c r="W218" s="28"/>
       <c r="X218" s="28"/>
@@ -17250,14 +17289,14 @@
       </c>
       <c r="J222" s="56">
         <f>SUM(G216:V216)</f>
-        <v>640362.48</v>
+        <v>1678133.69</v>
       </c>
       <c r="L222" s="63" t="s">
         <v>77</v>
       </c>
       <c r="M222" s="64">
         <f>(G222-J222)</f>
-        <v>1326213.1299999999</v>
+        <v>288441.91999999993</v>
       </c>
       <c r="O222" s="57" t="s">
         <v>92</v>
@@ -17306,54 +17345,54 @@
       </c>
     </row>
     <row r="225" spans="1:45" ht="18.600000000000001" thickBot="1">
-      <c r="A225" s="119" t="s">
+      <c r="A225" s="120" t="s">
         <v>202</v>
       </c>
-      <c r="B225" s="120"/>
-      <c r="C225" s="120"/>
-      <c r="D225" s="120"/>
-      <c r="E225" s="120"/>
-      <c r="F225" s="120"/>
-      <c r="G225" s="120"/>
-      <c r="H225" s="120"/>
-      <c r="I225" s="120"/>
-      <c r="J225" s="120"/>
-      <c r="K225" s="120"/>
-      <c r="L225" s="120"/>
-      <c r="M225" s="120"/>
-      <c r="N225" s="120"/>
-      <c r="O225" s="120"/>
-      <c r="P225" s="120"/>
-      <c r="Q225" s="120"/>
-      <c r="R225" s="120"/>
-      <c r="S225" s="120"/>
-      <c r="T225" s="120"/>
+      <c r="B225" s="121"/>
+      <c r="C225" s="121"/>
+      <c r="D225" s="121"/>
+      <c r="E225" s="121"/>
+      <c r="F225" s="121"/>
+      <c r="G225" s="121"/>
+      <c r="H225" s="121"/>
+      <c r="I225" s="121"/>
+      <c r="J225" s="121"/>
+      <c r="K225" s="121"/>
+      <c r="L225" s="121"/>
+      <c r="M225" s="121"/>
+      <c r="N225" s="121"/>
+      <c r="O225" s="121"/>
+      <c r="P225" s="121"/>
+      <c r="Q225" s="121"/>
+      <c r="R225" s="121"/>
+      <c r="S225" s="121"/>
+      <c r="T225" s="121"/>
       <c r="U225" s="7"/>
       <c r="V225" s="7"/>
       <c r="W225" s="7"/>
       <c r="X225" s="7"/>
       <c r="Y225" s="7"/>
       <c r="Z225" s="7"/>
-      <c r="AA225" s="115"/>
-      <c r="AB225" s="116"/>
+      <c r="AA225" s="116"/>
+      <c r="AB225" s="117"/>
       <c r="AC225" s="97"/>
-      <c r="AE225" s="117" t="s">
+      <c r="AE225" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="AF225" s="118"/>
-      <c r="AG225" s="118"/>
-      <c r="AH225" s="118"/>
-      <c r="AI225" s="118"/>
-      <c r="AJ225" s="118"/>
-      <c r="AK225" s="118"/>
-      <c r="AL225" s="118"/>
-      <c r="AM225" s="118"/>
-      <c r="AN225" s="118"/>
-      <c r="AO225" s="118"/>
-      <c r="AP225" s="118"/>
-      <c r="AQ225" s="118"/>
-      <c r="AR225" s="118"/>
-      <c r="AS225" s="118"/>
+      <c r="AF225" s="119"/>
+      <c r="AG225" s="119"/>
+      <c r="AH225" s="119"/>
+      <c r="AI225" s="119"/>
+      <c r="AJ225" s="119"/>
+      <c r="AK225" s="119"/>
+      <c r="AL225" s="119"/>
+      <c r="AM225" s="119"/>
+      <c r="AN225" s="119"/>
+      <c r="AO225" s="119"/>
+      <c r="AP225" s="119"/>
+      <c r="AQ225" s="119"/>
+      <c r="AR225" s="119"/>
+      <c r="AS225" s="119"/>
     </row>
     <row r="226" spans="1:45" ht="43.8" thickBot="1">
       <c r="A226" s="8" t="s">
@@ -17517,13 +17556,19 @@
       <c r="U227" s="11"/>
       <c r="V227" s="11"/>
       <c r="W227" s="72"/>
-      <c r="X227" s="74"/>
-      <c r="Y227" s="74"/>
+      <c r="X227" s="74">
+        <v>1000</v>
+      </c>
+      <c r="Y227" s="74">
+        <v>6400</v>
+      </c>
       <c r="Z227" s="11">
         <v>15000</v>
       </c>
       <c r="AA227" s="75"/>
-      <c r="AB227" s="75"/>
+      <c r="AB227" s="75">
+        <v>1000</v>
+      </c>
       <c r="AC227" s="75">
         <v>2500</v>
       </c>
@@ -17580,7 +17625,9 @@
       <c r="V228" s="11"/>
       <c r="W228" s="72"/>
       <c r="X228" s="74"/>
-      <c r="Y228" s="89"/>
+      <c r="Y228" s="89">
+        <v>8000</v>
+      </c>
       <c r="Z228" s="11">
         <v>15000</v>
       </c>
@@ -17705,7 +17752,9 @@
       <c r="Z230" s="11"/>
       <c r="AA230" s="75"/>
       <c r="AB230" s="75"/>
-      <c r="AC230" s="75"/>
+      <c r="AC230" s="75">
+        <v>2500</v>
+      </c>
       <c r="AE230" s="99" t="s">
         <v>117</v>
       </c>
@@ -17760,7 +17809,9 @@
       <c r="Z231" s="11"/>
       <c r="AA231" s="75"/>
       <c r="AB231" s="75"/>
-      <c r="AC231" s="75"/>
+      <c r="AC231" s="75">
+        <v>3500</v>
+      </c>
       <c r="AD231" s="93" t="s">
         <v>89</v>
       </c>
@@ -17861,7 +17912,9 @@
       <c r="Z232" s="11"/>
       <c r="AA232" s="75"/>
       <c r="AB232" s="75"/>
-      <c r="AC232" s="75"/>
+      <c r="AC232" s="75">
+        <v>150</v>
+      </c>
     </row>
     <row r="233" spans="1:45" ht="29.4" thickBot="1">
       <c r="A233" s="22">
@@ -17941,11 +17994,11 @@
       </c>
       <c r="X233" s="52">
         <f t="shared" ref="X233:AC233" si="121">SUM(X227:X232)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y233" s="52">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>14400</v>
       </c>
       <c r="Z233" s="52">
         <f t="shared" si="121"/>
@@ -17957,11 +18010,11 @@
       </c>
       <c r="AB233" s="52">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC233" s="52">
         <f t="shared" si="121"/>
-        <v>6500</v>
+        <v>12650</v>
       </c>
     </row>
     <row r="234" spans="1:45" ht="28.8">
@@ -18089,7 +18142,7 @@
       <c r="B236" s="23">
         <v>46326</v>
       </c>
-      <c r="C236" s="125" t="s">
+      <c r="C236" s="115" t="s">
         <v>203</v>
       </c>
       <c r="D236" s="22"/>
@@ -18146,7 +18199,7 @@
       <c r="B237" s="23">
         <v>46326</v>
       </c>
-      <c r="C237" s="125" t="s">
+      <c r="C237" s="115" t="s">
         <v>204</v>
       </c>
       <c r="D237" s="22"/>
@@ -18270,7 +18323,7 @@
       </c>
       <c r="S239" s="60">
         <f>SUM(X233:AC233)</f>
-        <v>42500</v>
+        <v>65050</v>
       </c>
       <c r="T239" s="32"/>
       <c r="U239" s="17"/>
@@ -18289,49 +18342,41 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="AA225:AB225"/>
-    <mergeCell ref="AE225:AS225"/>
-    <mergeCell ref="A225:D225"/>
-    <mergeCell ref="E225:H225"/>
-    <mergeCell ref="I225:L225"/>
-    <mergeCell ref="M225:P225"/>
-    <mergeCell ref="Q225:T225"/>
-    <mergeCell ref="AE103:AS103"/>
-    <mergeCell ref="AE120:AS120"/>
-    <mergeCell ref="AE37:AS37"/>
-    <mergeCell ref="AE54:AS54"/>
-    <mergeCell ref="AE69:AS69"/>
-    <mergeCell ref="AE87:AS87"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="M103:P103"/>
-    <mergeCell ref="Q103:T103"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q54:T54"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="M87:P87"/>
-    <mergeCell ref="Q87:T87"/>
+    <mergeCell ref="AA208:AB208"/>
+    <mergeCell ref="AE208:AS208"/>
+    <mergeCell ref="A208:D208"/>
+    <mergeCell ref="E208:H208"/>
+    <mergeCell ref="I208:L208"/>
+    <mergeCell ref="M208:P208"/>
+    <mergeCell ref="Q208:T208"/>
+    <mergeCell ref="AA192:AB192"/>
+    <mergeCell ref="AE192:AS192"/>
+    <mergeCell ref="A192:D192"/>
+    <mergeCell ref="E192:H192"/>
+    <mergeCell ref="I192:L192"/>
+    <mergeCell ref="M192:P192"/>
+    <mergeCell ref="Q192:T192"/>
+    <mergeCell ref="AA174:AB174"/>
+    <mergeCell ref="AE174:AS174"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="E174:H174"/>
+    <mergeCell ref="I174:L174"/>
+    <mergeCell ref="M174:P174"/>
+    <mergeCell ref="Q174:T174"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="AE158:AS158"/>
+    <mergeCell ref="AA158:AB158"/>
+    <mergeCell ref="Q158:T158"/>
+    <mergeCell ref="M158:P158"/>
+    <mergeCell ref="I158:L158"/>
+    <mergeCell ref="AA139:AB139"/>
+    <mergeCell ref="AE139:AS139"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="M139:P139"/>
+    <mergeCell ref="Q139:T139"/>
     <mergeCell ref="AA120:AB120"/>
     <mergeCell ref="AE2:AS2"/>
     <mergeCell ref="AE21:AS21"/>
@@ -18348,41 +18393,49 @@
     <mergeCell ref="I69:L69"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="AA139:AB139"/>
-    <mergeCell ref="AE139:AS139"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="M139:P139"/>
-    <mergeCell ref="Q139:T139"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="A158:D158"/>
-    <mergeCell ref="AE158:AS158"/>
-    <mergeCell ref="AA158:AB158"/>
-    <mergeCell ref="Q158:T158"/>
-    <mergeCell ref="M158:P158"/>
-    <mergeCell ref="I158:L158"/>
-    <mergeCell ref="AA174:AB174"/>
-    <mergeCell ref="AE174:AS174"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="E174:H174"/>
-    <mergeCell ref="I174:L174"/>
-    <mergeCell ref="M174:P174"/>
-    <mergeCell ref="Q174:T174"/>
-    <mergeCell ref="AA192:AB192"/>
-    <mergeCell ref="AE192:AS192"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="E192:H192"/>
-    <mergeCell ref="I192:L192"/>
-    <mergeCell ref="M192:P192"/>
-    <mergeCell ref="Q192:T192"/>
-    <mergeCell ref="AA208:AB208"/>
-    <mergeCell ref="AE208:AS208"/>
-    <mergeCell ref="A208:D208"/>
-    <mergeCell ref="E208:H208"/>
-    <mergeCell ref="I208:L208"/>
-    <mergeCell ref="M208:P208"/>
-    <mergeCell ref="Q208:T208"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="M87:P87"/>
+    <mergeCell ref="Q87:T87"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q54:T54"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="M103:P103"/>
+    <mergeCell ref="Q103:T103"/>
+    <mergeCell ref="AE103:AS103"/>
+    <mergeCell ref="AE120:AS120"/>
+    <mergeCell ref="AE37:AS37"/>
+    <mergeCell ref="AE54:AS54"/>
+    <mergeCell ref="AE69:AS69"/>
+    <mergeCell ref="AE87:AS87"/>
+    <mergeCell ref="AA225:AB225"/>
+    <mergeCell ref="AE225:AS225"/>
+    <mergeCell ref="A225:D225"/>
+    <mergeCell ref="E225:H225"/>
+    <mergeCell ref="I225:L225"/>
+    <mergeCell ref="M225:P225"/>
+    <mergeCell ref="Q225:T225"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18399,10 +18452,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:6" ht="15" thickBot="1">
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="124" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="124"/>
+      <c r="D1" s="125"/>
     </row>
     <row r="2" spans="3:6">
       <c r="C2" s="112" t="s">
